--- a/research/traditional_assets/database/data/portugal/portugal_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_packaging_container.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0823906646610362</v>
+        <v>0.08225319426524801</v>
       </c>
       <c r="C2">
-        <v>1437.908710435383</v>
+        <v>1426.329292582976</v>
       </c>
       <c r="D2">
-        <v>1330.708710435382</v>
+        <v>1333.673292582976</v>
       </c>
       <c r="E2">
-        <v>-346</v>
+        <v>-331.456</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.544</v>
       </c>
       <c r="G2">
         <v>107.2</v>
@@ -1451,28 +1451,28 @@
         <v>116.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7315632</v>
       </c>
       <c r="N2">
-        <v>116.1</v>
+        <v>115.3684368</v>
       </c>
       <c r="O2">
-        <v>24.381</v>
+        <v>24.227371728</v>
       </c>
       <c r="P2">
-        <v>91.71900000000001</v>
+        <v>91.141065072</v>
       </c>
       <c r="Q2">
-        <v>154.519</v>
+        <v>153.941065072</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0823906646610362</v>
+        <v>0.08268265077297779</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6218944784454993</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>158.7012577997363</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08225319426524801</v>
+        <v>0.08211572386945984</v>
       </c>
       <c r="C3">
-        <v>1426.329292582976</v>
+        <v>1414.763113346538</v>
       </c>
       <c r="D3">
-        <v>1333.673292582976</v>
+        <v>1336.651113346538</v>
       </c>
       <c r="E3">
-        <v>-331.456</v>
+        <v>-316.912</v>
       </c>
       <c r="F3">
-        <v>14.544</v>
+        <v>29.088</v>
       </c>
       <c r="G3">
         <v>107.2</v>
@@ -1533,28 +1533,28 @@
         <v>116.1</v>
       </c>
       <c r="M3">
-        <v>0.7315632</v>
+        <v>1.4631264</v>
       </c>
       <c r="N3">
-        <v>115.3684368</v>
+        <v>114.6368736</v>
       </c>
       <c r="O3">
-        <v>24.227371728</v>
+        <v>24.073743456</v>
       </c>
       <c r="P3">
-        <v>91.141065072</v>
+        <v>90.56313014400001</v>
       </c>
       <c r="Q3">
-        <v>153.941065072</v>
+        <v>153.363130144</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08268265077297779</v>
+        <v>0.08298059578516311</v>
       </c>
       <c r="T3">
-        <v>0.6218944784454993</v>
+        <v>0.6269182593851863</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>158.7012577997363</v>
+        <v>79.35062889986813</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08211572386945984</v>
+        <v>0.08197825347367166</v>
       </c>
       <c r="C4">
-        <v>1414.763113346538</v>
+        <v>1403.210261601909</v>
       </c>
       <c r="D4">
-        <v>1336.651113346538</v>
+        <v>1339.642261601909</v>
       </c>
       <c r="E4">
-        <v>-316.912</v>
+        <v>-302.368</v>
       </c>
       <c r="F4">
-        <v>29.088</v>
+        <v>43.632</v>
       </c>
       <c r="G4">
         <v>107.2</v>
@@ -1615,28 +1615,28 @@
         <v>116.1</v>
       </c>
       <c r="M4">
-        <v>1.4631264</v>
+        <v>2.1946896</v>
       </c>
       <c r="N4">
-        <v>114.6368736</v>
+        <v>113.9053104</v>
       </c>
       <c r="O4">
-        <v>24.073743456</v>
+        <v>23.920115184</v>
       </c>
       <c r="P4">
-        <v>90.56313014400001</v>
+        <v>89.98519521600001</v>
       </c>
       <c r="Q4">
-        <v>153.363130144</v>
+        <v>152.785195216</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08298059578516311</v>
+        <v>0.08328468399347594</v>
       </c>
       <c r="T4">
-        <v>0.6269182593851863</v>
+        <v>0.6320456234370319</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>79.35062889986813</v>
+        <v>52.90041926657875</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08197825347367166</v>
+        <v>0.08184078307788349</v>
       </c>
       <c r="C5">
-        <v>1403.210261601909</v>
+        <v>1391.670827022253</v>
       </c>
       <c r="D5">
-        <v>1339.642261601909</v>
+        <v>1342.646827022253</v>
       </c>
       <c r="E5">
-        <v>-302.368</v>
+        <v>-287.824</v>
       </c>
       <c r="F5">
-        <v>43.632</v>
+        <v>58.176</v>
       </c>
       <c r="G5">
         <v>107.2</v>
@@ -1697,28 +1697,28 @@
         <v>116.1</v>
       </c>
       <c r="M5">
-        <v>2.1946896</v>
+        <v>2.9262528</v>
       </c>
       <c r="N5">
-        <v>113.9053104</v>
+        <v>113.1737472</v>
       </c>
       <c r="O5">
-        <v>23.920115184</v>
+        <v>23.766486912</v>
       </c>
       <c r="P5">
-        <v>89.98519521600001</v>
+        <v>89.407260288</v>
       </c>
       <c r="Q5">
-        <v>152.785195216</v>
+        <v>152.207260288</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08328468399347594</v>
+        <v>0.0835951073727953</v>
       </c>
       <c r="T5">
-        <v>0.6320456234370319</v>
+        <v>0.6372798075732908</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>52.90041926657875</v>
+        <v>39.67531444993406</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08184078307788349</v>
+        <v>0.08170331268209532</v>
       </c>
       <c r="C6">
-        <v>1391.670827022253</v>
+        <v>1380.144900087027</v>
       </c>
       <c r="D6">
-        <v>1342.646827022253</v>
+        <v>1345.664900087027</v>
       </c>
       <c r="E6">
-        <v>-287.824</v>
+        <v>-273.28</v>
       </c>
       <c r="F6">
-        <v>58.176</v>
+        <v>72.72000000000001</v>
       </c>
       <c r="G6">
         <v>107.2</v>
@@ -1779,28 +1779,28 @@
         <v>116.1</v>
       </c>
       <c r="M6">
-        <v>2.9262528</v>
+        <v>3.657816</v>
       </c>
       <c r="N6">
-        <v>113.1737472</v>
+        <v>112.442184</v>
       </c>
       <c r="O6">
-        <v>23.766486912</v>
+        <v>23.61285864</v>
       </c>
       <c r="P6">
-        <v>89.407260288</v>
+        <v>88.82932536000001</v>
       </c>
       <c r="Q6">
-        <v>152.207260288</v>
+        <v>151.62932536</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0835951073727953</v>
+        <v>0.08391206598115297</v>
       </c>
       <c r="T6">
-        <v>0.6372798075732908</v>
+        <v>0.642624185059787</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.67531444993406</v>
+        <v>31.74025155994725</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08170331268209532</v>
+        <v>0.08156584228630713</v>
       </c>
       <c r="C7">
-        <v>1380.144900087027</v>
+        <v>1368.632572091055</v>
       </c>
       <c r="D7">
-        <v>1345.664900087027</v>
+        <v>1348.696572091055</v>
       </c>
       <c r="E7">
-        <v>-273.28</v>
+        <v>-258.736</v>
       </c>
       <c r="F7">
-        <v>72.72000000000001</v>
+        <v>87.26400000000001</v>
       </c>
       <c r="G7">
         <v>107.2</v>
@@ -1861,28 +1861,28 @@
         <v>116.1</v>
       </c>
       <c r="M7">
-        <v>3.657816</v>
+        <v>4.3893792</v>
       </c>
       <c r="N7">
-        <v>112.442184</v>
+        <v>111.7106208</v>
       </c>
       <c r="O7">
-        <v>23.61285864</v>
+        <v>23.459230368</v>
       </c>
       <c r="P7">
-        <v>88.82932536000001</v>
+        <v>88.25139043200001</v>
       </c>
       <c r="Q7">
-        <v>151.62932536</v>
+        <v>151.051390432</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08391206598115297</v>
+        <v>0.08423576838968844</v>
       </c>
       <c r="T7">
-        <v>0.642624185059787</v>
+        <v>0.6480822727055701</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.74025155994725</v>
+        <v>26.45020963328937</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08156584228630713</v>
+        <v>0.08142837189051898</v>
       </c>
       <c r="C8">
-        <v>1368.632572091056</v>
+        <v>1357.13393515374</v>
       </c>
       <c r="D8">
-        <v>1348.696572091055</v>
+        <v>1351.74193515374</v>
       </c>
       <c r="E8">
-        <v>-258.736</v>
+        <v>-244.192</v>
       </c>
       <c r="F8">
-        <v>87.264</v>
+        <v>101.808</v>
       </c>
       <c r="G8">
         <v>107.2</v>
@@ -1943,28 +1943,28 @@
         <v>116.1</v>
       </c>
       <c r="M8">
-        <v>4.3893792</v>
+        <v>5.1209424</v>
       </c>
       <c r="N8">
-        <v>111.7106208</v>
+        <v>110.9790576</v>
       </c>
       <c r="O8">
-        <v>23.459230368</v>
+        <v>23.305602096</v>
       </c>
       <c r="P8">
-        <v>88.25139043200001</v>
+        <v>87.673455504</v>
       </c>
       <c r="Q8">
-        <v>151.051390432</v>
+        <v>150.473455504</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08423576838968844</v>
+        <v>0.08456643214034298</v>
       </c>
       <c r="T8">
-        <v>0.6480822727055701</v>
+        <v>0.653657738580295</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.45020963328938</v>
+        <v>22.67160825710518</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08142837189051898</v>
+        <v>0.08129090149473078</v>
       </c>
       <c r="C9">
-        <v>1357.13393515374</v>
+        <v>1345.649082228391</v>
       </c>
       <c r="D9">
-        <v>1351.74193515374</v>
+        <v>1354.801082228391</v>
       </c>
       <c r="E9">
-        <v>-244.192</v>
+        <v>-229.648</v>
       </c>
       <c r="F9">
-        <v>101.808</v>
+        <v>116.352</v>
       </c>
       <c r="G9">
         <v>107.2</v>
@@ -2025,28 +2025,28 @@
         <v>116.1</v>
       </c>
       <c r="M9">
-        <v>5.120942400000001</v>
+        <v>5.8525056</v>
       </c>
       <c r="N9">
-        <v>110.9790576</v>
+        <v>110.2474944</v>
       </c>
       <c r="O9">
-        <v>23.305602096</v>
+        <v>23.151973824</v>
       </c>
       <c r="P9">
-        <v>87.673455504</v>
+        <v>87.09552057600001</v>
       </c>
       <c r="Q9">
-        <v>150.473455504</v>
+        <v>149.895520576</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08456643214034298</v>
+        <v>0.08490428423340303</v>
       </c>
       <c r="T9">
-        <v>0.653657738580295</v>
+        <v>0.6593544102349049</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.67160825710517</v>
+        <v>19.83765722496703</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08129090149473078</v>
+        <v>0.08115343109894263</v>
       </c>
       <c r="C10">
-        <v>1345.649082228391</v>
+        <v>1334.178107111681</v>
       </c>
       <c r="D10">
-        <v>1354.801082228391</v>
+        <v>1357.874107111681</v>
       </c>
       <c r="E10">
-        <v>-229.648</v>
+        <v>-215.104</v>
       </c>
       <c r="F10">
-        <v>116.352</v>
+        <v>130.896</v>
       </c>
       <c r="G10">
         <v>107.2</v>
@@ -2107,28 +2107,28 @@
         <v>116.1</v>
       </c>
       <c r="M10">
-        <v>5.8525056</v>
+        <v>6.584068800000001</v>
       </c>
       <c r="N10">
-        <v>110.2474944</v>
+        <v>109.5159312</v>
       </c>
       <c r="O10">
-        <v>23.151973824</v>
+        <v>22.998345552</v>
       </c>
       <c r="P10">
-        <v>87.09552057600001</v>
+        <v>86.51758564800001</v>
       </c>
       <c r="Q10">
-        <v>149.895520576</v>
+        <v>149.317585648</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08490428423340303</v>
+        <v>0.08524956164718969</v>
       </c>
       <c r="T10">
-        <v>0.6593544102349049</v>
+        <v>0.6651762834643417</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.83765722496703</v>
+        <v>17.63347308885958</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08115343109894263</v>
+        <v>0.08101596070315444</v>
       </c>
       <c r="C11">
-        <v>1334.178107111681</v>
+        <v>1322.721104453236</v>
       </c>
       <c r="D11">
-        <v>1357.874107111681</v>
+        <v>1360.961104453236</v>
       </c>
       <c r="E11">
-        <v>-215.104</v>
+        <v>-200.56</v>
       </c>
       <c r="F11">
-        <v>130.896</v>
+        <v>145.44</v>
       </c>
       <c r="G11">
         <v>107.2</v>
@@ -2189,28 +2189,28 @@
         <v>116.1</v>
       </c>
       <c r="M11">
-        <v>6.584068800000001</v>
+        <v>7.315632</v>
       </c>
       <c r="N11">
-        <v>109.5159312</v>
+        <v>108.784368</v>
       </c>
       <c r="O11">
-        <v>22.998345552</v>
+        <v>22.84471728</v>
       </c>
       <c r="P11">
-        <v>86.51758564800001</v>
+        <v>85.93965072000002</v>
       </c>
       <c r="Q11">
-        <v>149.317585648</v>
+        <v>148.73965072</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08524956164718969</v>
+        <v>0.08560251189239382</v>
       </c>
       <c r="T11">
-        <v>0.6651762834643417</v>
+        <v>0.6711275316544324</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.63347308885958</v>
+        <v>15.87012577997363</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08101596070315444</v>
+        <v>0.08087849030736625</v>
       </c>
       <c r="C12">
-        <v>1322.721104453236</v>
+        <v>1311.27816976535</v>
       </c>
       <c r="D12">
-        <v>1360.961104453236</v>
+        <v>1364.06216976535</v>
       </c>
       <c r="E12">
-        <v>-200.56</v>
+        <v>-186.016</v>
       </c>
       <c r="F12">
-        <v>145.44</v>
+        <v>159.984</v>
       </c>
       <c r="G12">
         <v>107.2</v>
@@ -2271,28 +2271,28 @@
         <v>116.1</v>
       </c>
       <c r="M12">
-        <v>7.315632000000001</v>
+        <v>8.047195200000001</v>
       </c>
       <c r="N12">
-        <v>108.784368</v>
+        <v>108.0528048</v>
       </c>
       <c r="O12">
-        <v>22.84471728</v>
+        <v>22.691089008</v>
       </c>
       <c r="P12">
-        <v>85.93965072</v>
+        <v>85.36171579200001</v>
       </c>
       <c r="Q12">
-        <v>148.73965072</v>
+        <v>148.161715792</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08560251189239382</v>
+        <v>0.0859633936037823</v>
       </c>
       <c r="T12">
-        <v>0.6711275316544324</v>
+        <v>0.6772125157589073</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.87012577997362</v>
+        <v>14.42738707270329</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08087849030736625</v>
+        <v>0.08074101991157807</v>
       </c>
       <c r="C13">
-        <v>1311.27816976535</v>
+        <v>1299.849399432836</v>
       </c>
       <c r="D13">
-        <v>1364.06216976535</v>
+        <v>1367.177399432836</v>
       </c>
       <c r="E13">
-        <v>-186.016</v>
+        <v>-171.472</v>
       </c>
       <c r="F13">
-        <v>159.984</v>
+        <v>174.528</v>
       </c>
       <c r="G13">
         <v>107.2</v>
@@ -2353,28 +2353,28 @@
         <v>116.1</v>
       </c>
       <c r="M13">
-        <v>8.047195200000001</v>
+        <v>8.778758399999999</v>
       </c>
       <c r="N13">
-        <v>108.0528048</v>
+        <v>107.3212416</v>
       </c>
       <c r="O13">
-        <v>22.691089008</v>
+        <v>22.537460736</v>
       </c>
       <c r="P13">
-        <v>85.36171579200001</v>
+        <v>84.78378086400001</v>
       </c>
       <c r="Q13">
-        <v>148.161715792</v>
+        <v>147.583780864</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0859633936037823</v>
+        <v>0.08633247717224782</v>
       </c>
       <c r="T13">
-        <v>0.6772125157589073</v>
+        <v>0.6834357949566657</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.42738707270329</v>
+        <v>13.22510481664469</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08074101991157807</v>
+        <v>0.0807575995157899</v>
       </c>
       <c r="C14">
-        <v>1299.849399432836</v>
+        <v>1284.92893309616</v>
       </c>
       <c r="D14">
-        <v>1367.177399432836</v>
+        <v>1366.80093309616</v>
       </c>
       <c r="E14">
-        <v>-171.472</v>
+        <v>-156.928</v>
       </c>
       <c r="F14">
-        <v>174.528</v>
+        <v>189.072</v>
       </c>
       <c r="G14">
         <v>107.2</v>
@@ -2435,45 +2435,45 @@
         <v>116.1</v>
       </c>
       <c r="M14">
-        <v>8.778758399999999</v>
+        <v>9.793929600000002</v>
       </c>
       <c r="N14">
-        <v>107.3212416</v>
+        <v>106.3060704</v>
       </c>
       <c r="O14">
-        <v>22.537460736</v>
+        <v>22.324274784</v>
       </c>
       <c r="P14">
-        <v>84.78378086400001</v>
+        <v>83.98179561600001</v>
       </c>
       <c r="Q14">
-        <v>147.583780864</v>
+        <v>146.781795616</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08633247717224782</v>
+        <v>0.08671004542044816</v>
       </c>
       <c r="T14">
-        <v>0.6834357949566657</v>
+        <v>0.6898021380440278</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.21</v>
       </c>
       <c r="W14">
-        <v>0.039737</v>
+        <v>0.040922</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.22510481664469</v>
+        <v>11.85428165626185</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0807575995157899</v>
+        <v>0.08063197912000174</v>
       </c>
       <c r="C15">
-        <v>1284.92893309616</v>
+        <v>1273.242520873777</v>
       </c>
       <c r="D15">
-        <v>1366.80093309616</v>
+        <v>1369.658520873777</v>
       </c>
       <c r="E15">
-        <v>-156.928</v>
+        <v>-142.384</v>
       </c>
       <c r="F15">
-        <v>189.072</v>
+        <v>203.616</v>
       </c>
       <c r="G15">
         <v>107.2</v>
@@ -2517,28 +2517,28 @@
         <v>116.1</v>
       </c>
       <c r="M15">
-        <v>9.793929600000002</v>
+        <v>10.5473088</v>
       </c>
       <c r="N15">
-        <v>106.3060704</v>
+        <v>105.5526912</v>
       </c>
       <c r="O15">
-        <v>22.324274784</v>
+        <v>22.166065152</v>
       </c>
       <c r="P15">
-        <v>83.98179561600001</v>
+        <v>83.38662604800001</v>
       </c>
       <c r="Q15">
-        <v>146.781795616</v>
+        <v>146.186626048</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08671004542044816</v>
+        <v>0.08709639432558341</v>
       </c>
       <c r="T15">
-        <v>0.6898021380440278</v>
+        <v>0.6963165356217936</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.85428165626185</v>
+        <v>11.00754725224315</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08063197912000174</v>
+        <v>0.08050635872421355</v>
       </c>
       <c r="C16">
-        <v>1273.242520873777</v>
+        <v>1261.568082474111</v>
       </c>
       <c r="D16">
-        <v>1369.658520873777</v>
+        <v>1372.528082474111</v>
       </c>
       <c r="E16">
-        <v>-142.384</v>
+        <v>-127.8399999999999</v>
       </c>
       <c r="F16">
-        <v>203.616</v>
+        <v>218.1600000000001</v>
       </c>
       <c r="G16">
         <v>107.2</v>
@@ -2599,28 +2599,28 @@
         <v>116.1</v>
       </c>
       <c r="M16">
-        <v>10.5473088</v>
+        <v>11.300688</v>
       </c>
       <c r="N16">
-        <v>105.5526912</v>
+        <v>104.799312</v>
       </c>
       <c r="O16">
-        <v>22.166065152</v>
+        <v>22.00785552</v>
       </c>
       <c r="P16">
-        <v>83.38662604800001</v>
+        <v>82.79145647999999</v>
       </c>
       <c r="Q16">
-        <v>146.186626048</v>
+        <v>145.59145648</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08709639432558341</v>
+        <v>0.08749183379319242</v>
       </c>
       <c r="T16">
-        <v>0.6963165356217936</v>
+        <v>0.7029842131425657</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.00754725224315</v>
+        <v>10.27371076876027</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08050635872421355</v>
+        <v>0.08059561832842536</v>
       </c>
       <c r="C17">
-        <v>1261.568082474111</v>
+        <v>1244.983880107262</v>
       </c>
       <c r="D17">
-        <v>1372.528082474111</v>
+        <v>1370.487880107262</v>
       </c>
       <c r="E17">
-        <v>-127.84</v>
+        <v>-113.296</v>
       </c>
       <c r="F17">
-        <v>218.16</v>
+        <v>232.704</v>
       </c>
       <c r="G17">
         <v>107.2</v>
@@ -2681,45 +2681,45 @@
         <v>116.1</v>
       </c>
       <c r="M17">
-        <v>11.300688</v>
+        <v>12.449664</v>
       </c>
       <c r="N17">
-        <v>104.799312</v>
+        <v>103.650336</v>
       </c>
       <c r="O17">
-        <v>22.00785552</v>
+        <v>21.76657056</v>
       </c>
       <c r="P17">
-        <v>82.79145648000001</v>
+        <v>81.88376544</v>
       </c>
       <c r="Q17">
-        <v>145.59145648</v>
+        <v>144.68376544</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08749183379319242</v>
+        <v>0.08789668848622068</v>
       </c>
       <c r="T17">
-        <v>0.7029842131425657</v>
+        <v>0.7098106448900228</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.21</v>
       </c>
       <c r="W17">
-        <v>0.040922</v>
+        <v>0.042265</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.27371076876028</v>
+        <v>9.325552882391044</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08059561832842536</v>
+        <v>0.0804834279326372</v>
       </c>
       <c r="C18">
-        <v>1244.983880107262</v>
+        <v>1233.005191520161</v>
       </c>
       <c r="D18">
-        <v>1370.487880107262</v>
+        <v>1373.053191520161</v>
       </c>
       <c r="E18">
-        <v>-113.296</v>
+        <v>-98.75199999999995</v>
       </c>
       <c r="F18">
-        <v>232.704</v>
+        <v>247.248</v>
       </c>
       <c r="G18">
         <v>107.2</v>
@@ -2763,28 +2763,28 @@
         <v>116.1</v>
       </c>
       <c r="M18">
-        <v>12.449664</v>
+        <v>13.227768</v>
       </c>
       <c r="N18">
-        <v>103.650336</v>
+        <v>102.872232</v>
       </c>
       <c r="O18">
-        <v>21.76657056</v>
+        <v>21.60316872</v>
       </c>
       <c r="P18">
-        <v>81.88376544</v>
+        <v>81.26906328000001</v>
       </c>
       <c r="Q18">
-        <v>144.68376544</v>
+        <v>144.06906328</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08789668848622068</v>
+        <v>0.08831129871402073</v>
       </c>
       <c r="T18">
-        <v>0.7098106448900228</v>
+        <v>0.716801568968744</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.325552882391044</v>
+        <v>8.776990948132745</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0804834279326372</v>
+        <v>0.08037123753684902</v>
       </c>
       <c r="C19">
-        <v>1233.005191520161</v>
+        <v>1221.036124563401</v>
       </c>
       <c r="D19">
-        <v>1373.053191520161</v>
+        <v>1375.628124563401</v>
       </c>
       <c r="E19">
-        <v>-98.75199999999995</v>
+        <v>-84.20799999999997</v>
       </c>
       <c r="F19">
-        <v>247.248</v>
+        <v>261.792</v>
       </c>
       <c r="G19">
         <v>107.2</v>
@@ -2845,28 +2845,28 @@
         <v>116.1</v>
       </c>
       <c r="M19">
-        <v>13.227768</v>
+        <v>14.005872</v>
       </c>
       <c r="N19">
-        <v>102.872232</v>
+        <v>102.094128</v>
       </c>
       <c r="O19">
-        <v>21.60316872</v>
+        <v>21.43976688</v>
       </c>
       <c r="P19">
-        <v>81.26906328000001</v>
+        <v>80.65436112</v>
       </c>
       <c r="Q19">
-        <v>144.06906328</v>
+        <v>143.45436112</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08831129871402073</v>
+        <v>0.08873602138640124</v>
       </c>
       <c r="T19">
-        <v>0.716801568968744</v>
+        <v>0.7239630033908485</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.776990948132745</v>
+        <v>8.289380339903149</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08037123753684902</v>
+        <v>0.08025904714106086</v>
       </c>
       <c r="C20">
-        <v>1221.036124563401</v>
+        <v>1209.076733469992</v>
       </c>
       <c r="D20">
-        <v>1375.628124563401</v>
+        <v>1378.212733469992</v>
       </c>
       <c r="E20">
-        <v>-84.20799999999997</v>
+        <v>-69.66399999999999</v>
       </c>
       <c r="F20">
-        <v>261.792</v>
+        <v>276.336</v>
       </c>
       <c r="G20">
         <v>107.2</v>
@@ -2927,28 +2927,28 @@
         <v>116.1</v>
       </c>
       <c r="M20">
-        <v>14.005872</v>
+        <v>14.783976</v>
       </c>
       <c r="N20">
-        <v>102.094128</v>
+        <v>101.316024</v>
       </c>
       <c r="O20">
-        <v>21.43976688</v>
+        <v>21.27636504</v>
       </c>
       <c r="P20">
-        <v>80.65436112</v>
+        <v>80.03965896000001</v>
       </c>
       <c r="Q20">
-        <v>143.45436112</v>
+        <v>142.83965896</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08873602138640124</v>
+        <v>0.08917123103834673</v>
       </c>
       <c r="T20">
-        <v>0.7239630033908485</v>
+        <v>0.7313012633542397</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.289380339903149</v>
+        <v>7.853097164118774</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08025904714106086</v>
+        <v>0.08027325674527268</v>
       </c>
       <c r="C21">
-        <v>1209.076733469992</v>
+        <v>1194.204839814567</v>
       </c>
       <c r="D21">
-        <v>1378.212733469992</v>
+        <v>1377.884839814567</v>
       </c>
       <c r="E21">
-        <v>-69.66399999999999</v>
+        <v>-55.11999999999995</v>
       </c>
       <c r="F21">
-        <v>276.336</v>
+        <v>290.8800000000001</v>
       </c>
       <c r="G21">
         <v>107.2</v>
@@ -3009,45 +3009,45 @@
         <v>116.1</v>
       </c>
       <c r="M21">
-        <v>14.783976</v>
+        <v>15.794784</v>
       </c>
       <c r="N21">
-        <v>101.316024</v>
+        <v>100.305216</v>
       </c>
       <c r="O21">
-        <v>21.27636504</v>
+        <v>21.06409536</v>
       </c>
       <c r="P21">
-        <v>80.03965896000001</v>
+        <v>79.24112064000001</v>
       </c>
       <c r="Q21">
-        <v>142.83965896</v>
+        <v>142.04112064</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08917123103834673</v>
+        <v>0.08961732093159085</v>
       </c>
       <c r="T21">
-        <v>0.7313012633542397</v>
+        <v>0.7388229798167156</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.21</v>
       </c>
       <c r="W21">
-        <v>0.042265</v>
+        <v>0.042897</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.853097164118774</v>
+        <v>7.350527870466603</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08027325674527268</v>
+        <v>0.0801673863494845</v>
       </c>
       <c r="C22">
-        <v>1194.204839814567</v>
+        <v>1182.107607540398</v>
       </c>
       <c r="D22">
-        <v>1377.884839814567</v>
+        <v>1380.331607540397</v>
       </c>
       <c r="E22">
-        <v>-55.11999999999995</v>
+        <v>-40.57599999999996</v>
       </c>
       <c r="F22">
-        <v>290.8800000000001</v>
+        <v>305.424</v>
       </c>
       <c r="G22">
         <v>107.2</v>
@@ -3091,28 +3091,28 @@
         <v>116.1</v>
       </c>
       <c r="M22">
-        <v>15.794784</v>
+        <v>16.5845232</v>
       </c>
       <c r="N22">
-        <v>100.305216</v>
+        <v>99.5154768</v>
       </c>
       <c r="O22">
-        <v>21.06409536</v>
+        <v>20.898250128</v>
       </c>
       <c r="P22">
-        <v>79.24112064000001</v>
+        <v>78.617226672</v>
       </c>
       <c r="Q22">
-        <v>142.04112064</v>
+        <v>141.417226672</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08961732093159085</v>
+        <v>0.0900747042398538</v>
       </c>
       <c r="T22">
-        <v>0.7388229798167156</v>
+        <v>0.7465351194807731</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.350527870466603</v>
+        <v>7.000502733777718</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0801673863494845</v>
+        <v>0.08006151595369632</v>
       </c>
       <c r="C23">
-        <v>1182.107607540398</v>
+        <v>1170.019080379786</v>
       </c>
       <c r="D23">
-        <v>1380.331607540397</v>
+        <v>1382.787080379786</v>
       </c>
       <c r="E23">
-        <v>-40.57599999999996</v>
+        <v>-26.03199999999998</v>
       </c>
       <c r="F23">
-        <v>305.424</v>
+        <v>319.968</v>
       </c>
       <c r="G23">
         <v>107.2</v>
@@ -3173,28 +3173,28 @@
         <v>116.1</v>
       </c>
       <c r="M23">
-        <v>16.5845232</v>
+        <v>17.3742624</v>
       </c>
       <c r="N23">
-        <v>99.5154768</v>
+        <v>98.7257376</v>
       </c>
       <c r="O23">
-        <v>20.898250128</v>
+        <v>20.732404896</v>
       </c>
       <c r="P23">
-        <v>78.617226672</v>
+        <v>77.99333270400001</v>
       </c>
       <c r="Q23">
-        <v>141.417226672</v>
+        <v>140.793332704</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0900747042398538</v>
+        <v>0.09054381532525169</v>
       </c>
       <c r="T23">
-        <v>0.7465351194807731</v>
+        <v>0.754445006315704</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.000502733777718</v>
+        <v>6.682298064060549</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08006151595369632</v>
+        <v>0.07995564555790814</v>
       </c>
       <c r="C24">
-        <v>1170.019080379786</v>
+        <v>1157.939304872117</v>
       </c>
       <c r="D24">
-        <v>1382.787080379786</v>
+        <v>1385.251304872117</v>
       </c>
       <c r="E24">
-        <v>-26.03199999999998</v>
+        <v>-11.48799999999994</v>
       </c>
       <c r="F24">
-        <v>319.968</v>
+        <v>334.5120000000001</v>
       </c>
       <c r="G24">
         <v>107.2</v>
@@ -3255,28 +3255,28 @@
         <v>116.1</v>
       </c>
       <c r="M24">
-        <v>17.3742624</v>
+        <v>18.1640016</v>
       </c>
       <c r="N24">
-        <v>98.7257376</v>
+        <v>97.9359984</v>
       </c>
       <c r="O24">
-        <v>20.732404896</v>
+        <v>20.566559664</v>
       </c>
       <c r="P24">
-        <v>77.99333270400001</v>
+        <v>77.36943873600001</v>
       </c>
       <c r="Q24">
-        <v>140.793332704</v>
+        <v>140.169438736</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09054381532525169</v>
+        <v>0.09102511111416642</v>
       </c>
       <c r="T24">
-        <v>0.754445006315704</v>
+        <v>0.762560344756737</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.682298064060549</v>
+        <v>6.391763365623134</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07995564555790814</v>
+        <v>0.07984977516211998</v>
       </c>
       <c r="C25">
-        <v>1157.939304872117</v>
+        <v>1145.868327889116</v>
       </c>
       <c r="D25">
-        <v>1385.251304872117</v>
+        <v>1387.724327889116</v>
       </c>
       <c r="E25">
-        <v>-11.48799999999994</v>
+        <v>3.05600000000004</v>
       </c>
       <c r="F25">
-        <v>334.5120000000001</v>
+        <v>349.056</v>
       </c>
       <c r="G25">
         <v>107.2</v>
@@ -3337,28 +3337,28 @@
         <v>116.1</v>
       </c>
       <c r="M25">
-        <v>18.1640016</v>
+        <v>18.9537408</v>
       </c>
       <c r="N25">
-        <v>97.9359984</v>
+        <v>97.1462592</v>
       </c>
       <c r="O25">
-        <v>20.566559664</v>
+        <v>20.400714432</v>
       </c>
       <c r="P25">
-        <v>77.36943873600001</v>
+        <v>76.745544768</v>
       </c>
       <c r="Q25">
-        <v>140.169438736</v>
+        <v>139.545544768</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09102511111416642</v>
+        <v>0.0915190725817368</v>
       </c>
       <c r="T25">
-        <v>0.762560344756737</v>
+        <v>0.7708892447356918</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.391763365623134</v>
+        <v>6.125439892055503</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07984977516211998</v>
+        <v>0.0799414047663318</v>
       </c>
       <c r="C26">
-        <v>1145.868327889116</v>
+        <v>1129.183441854029</v>
       </c>
       <c r="D26">
-        <v>1387.724327889116</v>
+        <v>1385.583441854029</v>
       </c>
       <c r="E26">
-        <v>3.055999999999983</v>
+        <v>17.60000000000002</v>
       </c>
       <c r="F26">
-        <v>349.056</v>
+        <v>363.6</v>
       </c>
       <c r="G26">
         <v>107.2</v>
@@ -3419,45 +3419,45 @@
         <v>116.1</v>
       </c>
       <c r="M26">
-        <v>18.9537408</v>
+        <v>20.10708</v>
       </c>
       <c r="N26">
-        <v>97.1462592</v>
+        <v>95.99292</v>
       </c>
       <c r="O26">
-        <v>20.400714432</v>
+        <v>20.1585132</v>
       </c>
       <c r="P26">
-        <v>76.745544768</v>
+        <v>75.8344068</v>
       </c>
       <c r="Q26">
-        <v>139.545544768</v>
+        <v>138.6344068</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0915190725817368</v>
+        <v>0.09202620635510905</v>
       </c>
       <c r="T26">
-        <v>0.7708892447356918</v>
+        <v>0.7794402487140853</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.21</v>
       </c>
       <c r="W26">
-        <v>0.042897</v>
+        <v>0.043687</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.125439892055504</v>
+        <v>5.774085545986786</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0799414047663318</v>
+        <v>0.07984343437054361</v>
       </c>
       <c r="C27">
-        <v>1129.183441854029</v>
+        <v>1116.928722514598</v>
       </c>
       <c r="D27">
-        <v>1385.583441854029</v>
+        <v>1387.872722514598</v>
       </c>
       <c r="E27">
-        <v>17.60000000000002</v>
+        <v>32.14400000000006</v>
       </c>
       <c r="F27">
-        <v>363.6</v>
+        <v>378.1440000000001</v>
       </c>
       <c r="G27">
         <v>107.2</v>
@@ -3501,28 +3501,28 @@
         <v>116.1</v>
       </c>
       <c r="M27">
-        <v>20.10708</v>
+        <v>20.9113632</v>
       </c>
       <c r="N27">
-        <v>95.99292</v>
+        <v>95.18863680000001</v>
       </c>
       <c r="O27">
-        <v>20.1585132</v>
+        <v>19.989613728</v>
       </c>
       <c r="P27">
-        <v>75.8344068</v>
+        <v>75.19902307200002</v>
       </c>
       <c r="Q27">
-        <v>138.6344068</v>
+        <v>137.999023072</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09202620635510905</v>
+        <v>0.09254704644668056</v>
       </c>
       <c r="T27">
-        <v>0.7794402487140853</v>
+        <v>0.7882223609081114</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.774085545986786</v>
+        <v>5.552005332679602</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07984343437054361</v>
+        <v>0.07974546397475545</v>
       </c>
       <c r="C28">
-        <v>1116.928722514598</v>
+        <v>1104.681580458567</v>
       </c>
       <c r="D28">
-        <v>1387.872722514598</v>
+        <v>1390.169580458567</v>
       </c>
       <c r="E28">
-        <v>32.14400000000006</v>
+        <v>46.68800000000005</v>
       </c>
       <c r="F28">
-        <v>378.1440000000001</v>
+        <v>392.688</v>
       </c>
       <c r="G28">
         <v>107.2</v>
@@ -3583,28 +3583,28 @@
         <v>116.1</v>
       </c>
       <c r="M28">
-        <v>20.9113632</v>
+        <v>21.7156464</v>
       </c>
       <c r="N28">
-        <v>95.18863680000001</v>
+        <v>94.3843536</v>
       </c>
       <c r="O28">
-        <v>19.989613728</v>
+        <v>19.820714256</v>
       </c>
       <c r="P28">
-        <v>75.19902307200002</v>
+        <v>74.56363934399999</v>
       </c>
       <c r="Q28">
-        <v>137.999023072</v>
+        <v>137.363639344</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09254704644668056</v>
+        <v>0.09308215612980197</v>
       </c>
       <c r="T28">
-        <v>0.7882223609081114</v>
+        <v>0.7972450789156723</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.552005332679602</v>
+        <v>5.34637550554332</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07974546397475545</v>
+        <v>0.07964749357896726</v>
       </c>
       <c r="C29">
-        <v>1104.681580458567</v>
+        <v>1092.442053368342</v>
       </c>
       <c r="D29">
-        <v>1390.169580458567</v>
+        <v>1392.474053368342</v>
       </c>
       <c r="E29">
-        <v>46.68800000000005</v>
+        <v>61.23200000000008</v>
       </c>
       <c r="F29">
-        <v>392.688</v>
+        <v>407.2320000000001</v>
       </c>
       <c r="G29">
         <v>107.2</v>
@@ -3665,28 +3665,28 @@
         <v>116.1</v>
       </c>
       <c r="M29">
-        <v>21.7156464</v>
+        <v>22.5199296</v>
       </c>
       <c r="N29">
-        <v>94.3843536</v>
+        <v>93.58007040000001</v>
       </c>
       <c r="O29">
-        <v>19.820714256</v>
+        <v>19.651814784</v>
       </c>
       <c r="P29">
-        <v>74.56363934399999</v>
+        <v>73.928255616</v>
       </c>
       <c r="Q29">
-        <v>137.363639344</v>
+        <v>136.728255616</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09308215612980197</v>
+        <v>0.09363212997078788</v>
       </c>
       <c r="T29">
-        <v>0.7972450789156723</v>
+        <v>0.8065184279789988</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.34637550554332</v>
+        <v>5.155433523202488</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07964749357896726</v>
+        <v>0.07954952318317909</v>
       </c>
       <c r="C30">
-        <v>1092.442053368342</v>
+        <v>1080.210179176605</v>
       </c>
       <c r="D30">
-        <v>1392.474053368342</v>
+        <v>1394.786179176605</v>
       </c>
       <c r="E30">
-        <v>61.23200000000008</v>
+        <v>75.77600000000007</v>
       </c>
       <c r="F30">
-        <v>407.2320000000001</v>
+        <v>421.7760000000001</v>
       </c>
       <c r="G30">
         <v>107.2</v>
@@ -3747,28 +3747,28 @@
         <v>116.1</v>
       </c>
       <c r="M30">
-        <v>22.5199296</v>
+        <v>23.32421280000001</v>
       </c>
       <c r="N30">
-        <v>93.58007040000001</v>
+        <v>92.7757872</v>
       </c>
       <c r="O30">
-        <v>19.651814784</v>
+        <v>19.482915312</v>
       </c>
       <c r="P30">
-        <v>73.928255616</v>
+        <v>73.29287188799999</v>
       </c>
       <c r="Q30">
-        <v>136.728255616</v>
+        <v>136.092871888</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09363212997078788</v>
+        <v>0.0941975960326466</v>
       </c>
       <c r="T30">
-        <v>0.8065184279789988</v>
+        <v>0.8160529981427006</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.155433523202488</v>
+        <v>4.977659953436884</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07954952318317909</v>
+        <v>0.0794515527873909</v>
       </c>
       <c r="C31">
-        <v>1080.210179176605</v>
+        <v>1067.9859960684</v>
       </c>
       <c r="D31">
-        <v>1394.786179176605</v>
+        <v>1397.1059960684</v>
       </c>
       <c r="E31">
-        <v>75.77600000000001</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F31">
-        <v>421.776</v>
+        <v>436.32</v>
       </c>
       <c r="G31">
         <v>107.2</v>
@@ -3829,28 +3829,28 @@
         <v>116.1</v>
       </c>
       <c r="M31">
-        <v>23.3242128</v>
+        <v>24.128496</v>
       </c>
       <c r="N31">
-        <v>92.77578720000001</v>
+        <v>91.97150400000001</v>
       </c>
       <c r="O31">
-        <v>19.482915312</v>
+        <v>19.31401584</v>
       </c>
       <c r="P31">
-        <v>73.29287188800001</v>
+        <v>72.65748816000001</v>
       </c>
       <c r="Q31">
-        <v>136.092871888</v>
+        <v>135.45748816</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0941975960326466</v>
+        <v>0.0947792182677013</v>
       </c>
       <c r="T31">
-        <v>0.8160529981427006</v>
+        <v>0.8258599845967939</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.977659953436886</v>
+        <v>4.811737954988989</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0794515527873909</v>
+        <v>0.07935358239160274</v>
       </c>
       <c r="C32">
-        <v>1067.9859960684</v>
+        <v>1055.769542483229</v>
       </c>
       <c r="D32">
-        <v>1397.1059960684</v>
+        <v>1399.433542483229</v>
       </c>
       <c r="E32">
-        <v>90.31999999999999</v>
+        <v>104.864</v>
       </c>
       <c r="F32">
-        <v>436.32</v>
+        <v>450.864</v>
       </c>
       <c r="G32">
         <v>107.2</v>
@@ -3911,28 +3911,28 @@
         <v>116.1</v>
       </c>
       <c r="M32">
-        <v>24.128496</v>
+        <v>24.9327792</v>
       </c>
       <c r="N32">
-        <v>91.97150400000001</v>
+        <v>91.16722080000001</v>
       </c>
       <c r="O32">
-        <v>19.31401584</v>
+        <v>19.145116368</v>
       </c>
       <c r="P32">
-        <v>72.65748816000001</v>
+        <v>72.02210443200001</v>
       </c>
       <c r="Q32">
-        <v>135.45748816</v>
+        <v>134.822104432</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0947792182677013</v>
+        <v>0.09537769911826485</v>
       </c>
       <c r="T32">
-        <v>0.8258599845967939</v>
+        <v>0.8359512315278176</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.811737954988989</v>
+        <v>4.656520601602248</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07935358239160274</v>
+        <v>0.07925561199581457</v>
       </c>
       <c r="C33">
-        <v>1055.769542483229</v>
+        <v>1043.560857117182</v>
       </c>
       <c r="D33">
-        <v>1399.433542483229</v>
+        <v>1401.768857117182</v>
       </c>
       <c r="E33">
-        <v>104.864</v>
+        <v>119.408</v>
       </c>
       <c r="F33">
-        <v>450.864</v>
+        <v>465.408</v>
       </c>
       <c r="G33">
         <v>107.2</v>
@@ -3993,28 +3993,28 @@
         <v>116.1</v>
       </c>
       <c r="M33">
-        <v>24.9327792</v>
+        <v>25.7370624</v>
       </c>
       <c r="N33">
-        <v>91.16722080000001</v>
+        <v>90.36293760000001</v>
       </c>
       <c r="O33">
-        <v>19.145116368</v>
+        <v>18.976216896</v>
       </c>
       <c r="P33">
-        <v>72.02210443200001</v>
+        <v>71.38672070400001</v>
       </c>
       <c r="Q33">
-        <v>134.822104432</v>
+        <v>134.186720704</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09537769911826485</v>
+        <v>0.09599378234678613</v>
       </c>
       <c r="T33">
-        <v>0.8359512315278176</v>
+        <v>0.8463392798391653</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.656520601602248</v>
+        <v>4.511004332802177</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07925561199581457</v>
+        <v>0.07980939160002638</v>
       </c>
       <c r="C34">
-        <v>1043.560857117182</v>
+        <v>1015.917974179143</v>
       </c>
       <c r="D34">
-        <v>1401.768857117182</v>
+        <v>1388.669974179143</v>
       </c>
       <c r="E34">
-        <v>119.408</v>
+        <v>133.9520000000001</v>
       </c>
       <c r="F34">
-        <v>465.408</v>
+        <v>479.9520000000001</v>
       </c>
       <c r="G34">
         <v>107.2</v>
@@ -4075,45 +4075,45 @@
         <v>116.1</v>
       </c>
       <c r="M34">
-        <v>25.7370624</v>
+        <v>27.7412256</v>
       </c>
       <c r="N34">
-        <v>90.36293760000001</v>
+        <v>88.3587744</v>
       </c>
       <c r="O34">
-        <v>18.976216896</v>
+        <v>18.555342624</v>
       </c>
       <c r="P34">
-        <v>71.38672070400001</v>
+        <v>69.803431776</v>
       </c>
       <c r="Q34">
-        <v>134.186720704</v>
+        <v>132.603431776</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09599378234678613</v>
+        <v>0.09662825611944237</v>
       </c>
       <c r="T34">
-        <v>0.8463392798391653</v>
+        <v>0.8570374191448817</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.21</v>
       </c>
       <c r="W34">
-        <v>0.043687</v>
+        <v>0.04566200000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.511004332802177</v>
+        <v>4.185107092024081</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07980939160002638</v>
+        <v>0.0797311712042382</v>
       </c>
       <c r="C35">
-        <v>1015.917974179143</v>
+        <v>1003.209301609207</v>
       </c>
       <c r="D35">
-        <v>1388.669974179143</v>
+        <v>1390.505301609207</v>
       </c>
       <c r="E35">
-        <v>133.9520000000001</v>
+        <v>148.4960000000001</v>
       </c>
       <c r="F35">
-        <v>479.9520000000001</v>
+        <v>494.4960000000001</v>
       </c>
       <c r="G35">
         <v>107.2</v>
@@ -4157,28 +4157,28 @@
         <v>116.1</v>
       </c>
       <c r="M35">
-        <v>27.7412256</v>
+        <v>28.58186880000001</v>
       </c>
       <c r="N35">
-        <v>88.3587744</v>
+        <v>87.5181312</v>
       </c>
       <c r="O35">
-        <v>18.555342624</v>
+        <v>18.378807552</v>
       </c>
       <c r="P35">
-        <v>69.803431776</v>
+        <v>69.139323648</v>
       </c>
       <c r="Q35">
-        <v>132.603431776</v>
+        <v>131.939323648</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09662825611944237</v>
+        <v>0.0972819563700579</v>
       </c>
       <c r="T35">
-        <v>0.8570374191448817</v>
+        <v>0.8680597444901654</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.185107092024081</v>
+        <v>4.062015706964549</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0797311712042382</v>
+        <v>0.08062070080845003</v>
       </c>
       <c r="C36">
-        <v>1003.209301609207</v>
+        <v>968.0756623151909</v>
       </c>
       <c r="D36">
-        <v>1390.505301609207</v>
+        <v>1369.915662315191</v>
       </c>
       <c r="E36">
-        <v>148.4960000000001</v>
+        <v>163.0400000000001</v>
       </c>
       <c r="F36">
-        <v>494.4960000000001</v>
+        <v>509.0400000000001</v>
       </c>
       <c r="G36">
         <v>107.2</v>
@@ -4239,45 +4239,45 @@
         <v>116.1</v>
       </c>
       <c r="M36">
-        <v>28.58186880000001</v>
+        <v>31.204152</v>
       </c>
       <c r="N36">
-        <v>87.5181312</v>
+        <v>84.895848</v>
       </c>
       <c r="O36">
-        <v>18.378807552</v>
+        <v>17.82812808</v>
       </c>
       <c r="P36">
-        <v>69.139323648</v>
+        <v>67.06771992</v>
       </c>
       <c r="Q36">
-        <v>131.939323648</v>
+        <v>129.86771992</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0972819563700579</v>
+        <v>0.09795577047453852</v>
       </c>
       <c r="T36">
-        <v>0.8680597444901654</v>
+        <v>0.8794212183076114</v>
       </c>
       <c r="U36">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V36">
         <v>0.21</v>
       </c>
       <c r="W36">
-        <v>0.04566200000000001</v>
+        <v>0.048427</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.062015706964549</v>
+        <v>3.720658712340588</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08062070080845003</v>
+        <v>0.08057013041266185</v>
       </c>
       <c r="C37">
-        <v>968.0756623151909</v>
+        <v>954.6858371804585</v>
       </c>
       <c r="D37">
-        <v>1369.915662315191</v>
+        <v>1371.069837180459</v>
       </c>
       <c r="E37">
-        <v>163.0400000000001</v>
+        <v>177.5840000000001</v>
       </c>
       <c r="F37">
-        <v>509.0400000000001</v>
+        <v>523.5840000000001</v>
       </c>
       <c r="G37">
         <v>107.2</v>
@@ -4321,28 +4321,28 @@
         <v>116.1</v>
       </c>
       <c r="M37">
-        <v>31.204152</v>
+        <v>32.09569920000001</v>
       </c>
       <c r="N37">
-        <v>84.895848</v>
+        <v>84.00430080000001</v>
       </c>
       <c r="O37">
-        <v>17.82812808</v>
+        <v>17.640903168</v>
       </c>
       <c r="P37">
-        <v>67.06771992</v>
+        <v>66.36339763200002</v>
       </c>
       <c r="Q37">
-        <v>129.86771992</v>
+        <v>129.163397632</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09795577047453852</v>
+        <v>0.09865064126978416</v>
       </c>
       <c r="T37">
-        <v>0.8794212183076114</v>
+        <v>0.8911377381818528</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.720658712340588</v>
+        <v>3.617307081442239</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08057013041266185</v>
+        <v>0.08051956001687369</v>
       </c>
       <c r="C38">
-        <v>954.6858371804585</v>
+        <v>941.297958505546</v>
       </c>
       <c r="D38">
-        <v>1371.069837180459</v>
+        <v>1372.225958505546</v>
       </c>
       <c r="E38">
-        <v>177.5840000000001</v>
+        <v>192.128</v>
       </c>
       <c r="F38">
-        <v>523.5840000000001</v>
+        <v>538.128</v>
       </c>
       <c r="G38">
         <v>107.2</v>
@@ -4403,28 +4403,28 @@
         <v>116.1</v>
       </c>
       <c r="M38">
-        <v>32.09569920000001</v>
+        <v>32.9872464</v>
       </c>
       <c r="N38">
-        <v>84.00430080000001</v>
+        <v>83.1127536</v>
       </c>
       <c r="O38">
-        <v>17.640903168</v>
+        <v>17.453678256</v>
       </c>
       <c r="P38">
-        <v>66.36339763200002</v>
+        <v>65.659075344</v>
       </c>
       <c r="Q38">
-        <v>129.163397632</v>
+        <v>128.459075344</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09865064126978415</v>
+        <v>0.09936757145535505</v>
       </c>
       <c r="T38">
-        <v>0.8911377381818526</v>
+        <v>0.9032262110679746</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.617307081442239</v>
+        <v>3.519542025187043</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08051956001687369</v>
+        <v>0.0813095496210855</v>
       </c>
       <c r="C39">
-        <v>941.297958505546</v>
+        <v>908.9132914828497</v>
       </c>
       <c r="D39">
-        <v>1372.225958505546</v>
+        <v>1354.38529148285</v>
       </c>
       <c r="E39">
-        <v>192.128</v>
+        <v>206.672</v>
       </c>
       <c r="F39">
-        <v>538.128</v>
+        <v>552.672</v>
       </c>
       <c r="G39">
         <v>107.2</v>
@@ -4485,45 +4485,45 @@
         <v>116.1</v>
       </c>
       <c r="M39">
-        <v>32.9872464</v>
+        <v>35.42627520000001</v>
       </c>
       <c r="N39">
-        <v>83.1127536</v>
+        <v>80.6737248</v>
       </c>
       <c r="O39">
-        <v>17.453678256</v>
+        <v>16.941482208</v>
       </c>
       <c r="P39">
-        <v>65.659075344</v>
+        <v>63.73224259200001</v>
       </c>
       <c r="Q39">
-        <v>128.459075344</v>
+        <v>126.532242592</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09936757145535505</v>
+        <v>0.1001076284211057</v>
       </c>
       <c r="T39">
-        <v>0.9032262110679746</v>
+        <v>0.9157046346923587</v>
       </c>
       <c r="U39">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.21</v>
       </c>
       <c r="W39">
-        <v>0.048427</v>
+        <v>0.050639</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.519542025187043</v>
+        <v>3.277228535728193</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0813095496210855</v>
+        <v>0.08128109922529733</v>
       </c>
       <c r="C40">
-        <v>908.9132914828497</v>
+        <v>895.0037423802866</v>
       </c>
       <c r="D40">
-        <v>1354.38529148285</v>
+        <v>1355.019742380287</v>
       </c>
       <c r="E40">
-        <v>206.672</v>
+        <v>221.216</v>
       </c>
       <c r="F40">
-        <v>552.672</v>
+        <v>567.216</v>
       </c>
       <c r="G40">
         <v>107.2</v>
@@ -4567,28 +4567,28 @@
         <v>116.1</v>
       </c>
       <c r="M40">
-        <v>35.42627520000001</v>
+        <v>36.3585456</v>
       </c>
       <c r="N40">
-        <v>80.6737248</v>
+        <v>79.74145440000001</v>
       </c>
       <c r="O40">
-        <v>16.941482208</v>
+        <v>16.745705424</v>
       </c>
       <c r="P40">
-        <v>63.73224259200001</v>
+        <v>62.99574897600001</v>
       </c>
       <c r="Q40">
-        <v>126.532242592</v>
+        <v>125.795748976</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1001076284211057</v>
+        <v>0.1008719495496678</v>
       </c>
       <c r="T40">
-        <v>0.9157046346923587</v>
+        <v>0.9285921869601651</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.277228535728193</v>
+        <v>3.193197034812086</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08128109922529733</v>
+        <v>0.08125264882950915</v>
       </c>
       <c r="C41">
-        <v>895.0037423802866</v>
+        <v>881.0947879631398</v>
       </c>
       <c r="D41">
-        <v>1355.019742380287</v>
+        <v>1355.65478796314</v>
       </c>
       <c r="E41">
-        <v>221.216</v>
+        <v>235.7600000000001</v>
       </c>
       <c r="F41">
-        <v>567.216</v>
+        <v>581.7600000000001</v>
       </c>
       <c r="G41">
         <v>107.2</v>
@@ -4649,28 +4649,28 @@
         <v>116.1</v>
       </c>
       <c r="M41">
-        <v>36.3585456</v>
+        <v>37.29081600000001</v>
       </c>
       <c r="N41">
-        <v>79.74145440000001</v>
+        <v>78.809184</v>
       </c>
       <c r="O41">
-        <v>16.745705424</v>
+        <v>16.54992864</v>
       </c>
       <c r="P41">
-        <v>62.99574897600001</v>
+        <v>62.25925536</v>
       </c>
       <c r="Q41">
-        <v>125.795748976</v>
+        <v>125.05925536</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1008719495496678</v>
+        <v>0.1016617480491819</v>
       </c>
       <c r="T41">
-        <v>0.9285921869601651</v>
+        <v>0.9419093243035651</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.193197034812086</v>
+        <v>3.113367108941783</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08125264882950915</v>
+        <v>0.08122419843372097</v>
       </c>
       <c r="C42">
-        <v>881.0947879631398</v>
+        <v>867.1864290679202</v>
       </c>
       <c r="D42">
-        <v>1355.65478796314</v>
+        <v>1356.29042906792</v>
       </c>
       <c r="E42">
-        <v>235.7600000000001</v>
+        <v>250.3040000000001</v>
       </c>
       <c r="F42">
-        <v>581.7600000000001</v>
+        <v>596.3040000000001</v>
       </c>
       <c r="G42">
         <v>107.2</v>
@@ -4731,28 +4731,28 @@
         <v>116.1</v>
       </c>
       <c r="M42">
-        <v>37.29081600000001</v>
+        <v>38.22308640000001</v>
       </c>
       <c r="N42">
-        <v>78.809184</v>
+        <v>77.87691359999999</v>
       </c>
       <c r="O42">
-        <v>16.54992864</v>
+        <v>16.354151856</v>
       </c>
       <c r="P42">
-        <v>62.25925536</v>
+        <v>61.52276174399999</v>
       </c>
       <c r="Q42">
-        <v>125.05925536</v>
+        <v>124.322761744</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1016617480491819</v>
+        <v>0.1024783193791881</v>
       </c>
       <c r="T42">
-        <v>0.9419093243035651</v>
+        <v>0.955677890031487</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.113367108941783</v>
+        <v>3.037431325796861</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08122419843372097</v>
+        <v>0.08378378803793281</v>
       </c>
       <c r="C43">
-        <v>867.1864290679202</v>
+        <v>797.7448366412833</v>
       </c>
       <c r="D43">
-        <v>1356.29042906792</v>
+        <v>1301.392836641283</v>
       </c>
       <c r="E43">
-        <v>250.3040000000001</v>
+        <v>264.8480000000001</v>
       </c>
       <c r="F43">
-        <v>596.3040000000001</v>
+        <v>610.8480000000001</v>
       </c>
       <c r="G43">
         <v>107.2</v>
@@ -4813,45 +4813,45 @@
         <v>116.1</v>
       </c>
       <c r="M43">
-        <v>38.22308640000001</v>
+        <v>43.91997120000001</v>
       </c>
       <c r="N43">
-        <v>77.87691359999999</v>
+        <v>72.1800288</v>
       </c>
       <c r="O43">
-        <v>16.354151856</v>
+        <v>15.157806048</v>
       </c>
       <c r="P43">
-        <v>61.52276174399999</v>
+        <v>57.022222752</v>
       </c>
       <c r="Q43">
-        <v>124.322761744</v>
+        <v>119.822222752</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1024783193791881</v>
+        <v>0.1033230483412635</v>
       </c>
       <c r="T43">
-        <v>0.955677890031487</v>
+        <v>0.9699212338879581</v>
       </c>
       <c r="U43">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V43">
         <v>0.21</v>
       </c>
       <c r="W43">
-        <v>0.050639</v>
+        <v>0.056801</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.037431325796861</v>
+        <v>2.643444356356955</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08378378803793281</v>
+        <v>0.08381695764214463</v>
       </c>
       <c r="C44">
-        <v>797.7448366412833</v>
+        <v>782.5185745763956</v>
       </c>
       <c r="D44">
-        <v>1301.392836641283</v>
+        <v>1300.710574576396</v>
       </c>
       <c r="E44">
-        <v>264.8480000000001</v>
+        <v>279.3920000000001</v>
       </c>
       <c r="F44">
-        <v>610.8480000000001</v>
+        <v>625.3920000000001</v>
       </c>
       <c r="G44">
         <v>107.2</v>
@@ -4895,28 +4895,28 @@
         <v>116.1</v>
       </c>
       <c r="M44">
-        <v>43.91997120000001</v>
+        <v>44.96568480000001</v>
       </c>
       <c r="N44">
-        <v>72.1800288</v>
+        <v>71.1343152</v>
       </c>
       <c r="O44">
-        <v>15.157806048</v>
+        <v>14.938206192</v>
       </c>
       <c r="P44">
-        <v>57.022222752</v>
+        <v>56.196109008</v>
       </c>
       <c r="Q44">
-        <v>119.822222752</v>
+        <v>118.996109008</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1033230483412634</v>
+        <v>0.1041974169160432</v>
       </c>
       <c r="T44">
-        <v>0.969921233887958</v>
+        <v>0.9846643441955333</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.643444356356955</v>
+        <v>2.581968906209119</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08381695764214463</v>
+        <v>0.08385012724635646</v>
       </c>
       <c r="C45">
-        <v>782.5185745763956</v>
+        <v>767.2930274956519</v>
       </c>
       <c r="D45">
-        <v>1300.710574576396</v>
+        <v>1300.029027495652</v>
       </c>
       <c r="E45">
-        <v>279.3920000000001</v>
+        <v>293.936</v>
       </c>
       <c r="F45">
-        <v>625.3920000000001</v>
+        <v>639.936</v>
       </c>
       <c r="G45">
         <v>107.2</v>
@@ -4977,28 +4977,28 @@
         <v>116.1</v>
       </c>
       <c r="M45">
-        <v>44.96568480000001</v>
+        <v>46.0113984</v>
       </c>
       <c r="N45">
-        <v>71.1343152</v>
+        <v>70.0886016</v>
       </c>
       <c r="O45">
-        <v>14.938206192</v>
+        <v>14.718606336</v>
       </c>
       <c r="P45">
-        <v>56.196109008</v>
+        <v>55.369995264</v>
       </c>
       <c r="Q45">
-        <v>118.996109008</v>
+        <v>118.169995264</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1041974169160432</v>
+        <v>0.1051030129399222</v>
       </c>
       <c r="T45">
-        <v>0.9846643441955333</v>
+        <v>0.9999339941569506</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.581968906209119</v>
+        <v>2.523287794704366</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08385012724635646</v>
+        <v>0.08526974685056829</v>
       </c>
       <c r="C46">
-        <v>767.2930274956519</v>
+        <v>724.2343698148193</v>
       </c>
       <c r="D46">
-        <v>1300.029027495652</v>
+        <v>1271.514369814819</v>
       </c>
       <c r="E46">
-        <v>293.936</v>
+        <v>308.48</v>
       </c>
       <c r="F46">
-        <v>639.936</v>
+        <v>654.48</v>
       </c>
       <c r="G46">
         <v>107.2</v>
@@ -5059,45 +5059,45 @@
         <v>116.1</v>
       </c>
       <c r="M46">
-        <v>46.0113984</v>
+        <v>49.60958400000001</v>
       </c>
       <c r="N46">
-        <v>70.0886016</v>
+        <v>66.49041600000001</v>
       </c>
       <c r="O46">
-        <v>14.718606336</v>
+        <v>13.96298736</v>
       </c>
       <c r="P46">
-        <v>55.369995264</v>
+        <v>52.52742864000001</v>
       </c>
       <c r="Q46">
-        <v>118.169995264</v>
+        <v>115.32742864</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1051030129399222</v>
+        <v>0.106041539728306</v>
       </c>
       <c r="T46">
-        <v>0.9999339941569506</v>
+        <v>1.015758904116965</v>
       </c>
       <c r="U46">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.21</v>
       </c>
       <c r="W46">
-        <v>0.056801</v>
+        <v>0.059882</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.523287794704366</v>
+        <v>2.340273605196932</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08526974685056829</v>
+        <v>0.0853337264547801</v>
       </c>
       <c r="C47">
-        <v>724.2343698148193</v>
+        <v>708.4346959633108</v>
       </c>
       <c r="D47">
-        <v>1271.514369814819</v>
+        <v>1270.258695963311</v>
       </c>
       <c r="E47">
-        <v>308.48</v>
+        <v>323.0240000000001</v>
       </c>
       <c r="F47">
-        <v>654.48</v>
+        <v>669.0240000000001</v>
       </c>
       <c r="G47">
         <v>107.2</v>
@@ -5141,28 +5141,28 @@
         <v>116.1</v>
       </c>
       <c r="M47">
-        <v>49.60958400000001</v>
+        <v>50.71201920000001</v>
       </c>
       <c r="N47">
-        <v>66.49041600000001</v>
+        <v>65.38798079999999</v>
       </c>
       <c r="O47">
-        <v>13.96298736</v>
+        <v>13.731475968</v>
       </c>
       <c r="P47">
-        <v>52.52742864000001</v>
+        <v>51.656504832</v>
       </c>
       <c r="Q47">
-        <v>115.32742864</v>
+        <v>114.456504832</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.106041539728306</v>
+        <v>0.1070148267681113</v>
       </c>
       <c r="T47">
-        <v>1.015758904116965</v>
+        <v>1.032169921853276</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.340273605196932</v>
+        <v>2.289398092040476</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0853337264547801</v>
+        <v>0.08539770605899194</v>
       </c>
       <c r="C48">
-        <v>708.4346959633108</v>
+        <v>692.6374997264019</v>
       </c>
       <c r="D48">
-        <v>1270.258695963311</v>
+        <v>1269.005499726402</v>
       </c>
       <c r="E48">
-        <v>323.0240000000001</v>
+        <v>337.5680000000001</v>
       </c>
       <c r="F48">
-        <v>669.0240000000001</v>
+        <v>683.5680000000001</v>
       </c>
       <c r="G48">
         <v>107.2</v>
@@ -5223,28 +5223,28 @@
         <v>116.1</v>
       </c>
       <c r="M48">
-        <v>50.71201920000001</v>
+        <v>51.81445440000001</v>
       </c>
       <c r="N48">
-        <v>65.38798079999999</v>
+        <v>64.28554560000001</v>
       </c>
       <c r="O48">
-        <v>13.731475968</v>
+        <v>13.499964576</v>
       </c>
       <c r="P48">
-        <v>51.656504832</v>
+        <v>50.78558102400001</v>
       </c>
       <c r="Q48">
-        <v>114.456504832</v>
+        <v>113.585581024</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1070148267681113</v>
+        <v>0.1080248416207395</v>
       </c>
       <c r="T48">
-        <v>1.032169921853276</v>
+        <v>1.04920022327775</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.289398092040476</v>
+        <v>2.240687494337487</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08539770605899194</v>
+        <v>0.08546168566320377</v>
       </c>
       <c r="C49">
-        <v>692.6374997264019</v>
+        <v>676.842773778317</v>
       </c>
       <c r="D49">
-        <v>1269.005499726402</v>
+        <v>1267.754773778317</v>
       </c>
       <c r="E49">
-        <v>337.5680000000001</v>
+        <v>352.1120000000001</v>
       </c>
       <c r="F49">
-        <v>683.5680000000001</v>
+        <v>698.1120000000001</v>
       </c>
       <c r="G49">
         <v>107.2</v>
@@ -5305,28 +5305,28 @@
         <v>116.1</v>
       </c>
       <c r="M49">
-        <v>51.81445440000001</v>
+        <v>52.91688960000001</v>
       </c>
       <c r="N49">
-        <v>64.28554560000001</v>
+        <v>63.1831104</v>
       </c>
       <c r="O49">
-        <v>13.499964576</v>
+        <v>13.268453184</v>
       </c>
       <c r="P49">
-        <v>50.78558102400001</v>
+        <v>49.91465721599999</v>
       </c>
       <c r="Q49">
-        <v>113.585581024</v>
+        <v>112.714657216</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1080248416207395</v>
+        <v>0.1090737031984688</v>
       </c>
       <c r="T49">
-        <v>1.04920022327775</v>
+        <v>1.066885536295473</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.240687494337487</v>
+        <v>2.194006504872123</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08546168566320375</v>
+        <v>0.08552566526741559</v>
       </c>
       <c r="C50">
-        <v>676.8427737783173</v>
+        <v>661.0505108221317</v>
       </c>
       <c r="D50">
-        <v>1267.754773778317</v>
+        <v>1266.506510822132</v>
       </c>
       <c r="E50">
-        <v>352.112</v>
+        <v>366.6560000000001</v>
       </c>
       <c r="F50">
-        <v>698.112</v>
+        <v>712.6560000000001</v>
       </c>
       <c r="G50">
         <v>107.2</v>
@@ -5387,28 +5387,28 @@
         <v>116.1</v>
       </c>
       <c r="M50">
-        <v>52.9168896</v>
+        <v>54.01932480000001</v>
       </c>
       <c r="N50">
-        <v>63.1831104</v>
+        <v>62.0806752</v>
       </c>
       <c r="O50">
-        <v>13.268453184</v>
+        <v>13.036941792</v>
       </c>
       <c r="P50">
-        <v>49.914657216</v>
+        <v>49.043733408</v>
       </c>
       <c r="Q50">
-        <v>112.714657216</v>
+        <v>111.843733408</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1090737031984687</v>
+        <v>0.1101636966027756</v>
       </c>
       <c r="T50">
-        <v>1.066885536295472</v>
+        <v>1.085264391000165</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.194006504872123</v>
+        <v>2.149230861915549</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08552566526741559</v>
+        <v>0.0855896448716274</v>
       </c>
       <c r="C51">
-        <v>661.0505108221317</v>
+        <v>645.2607035896333</v>
       </c>
       <c r="D51">
-        <v>1266.506510822132</v>
+        <v>1265.260703589633</v>
       </c>
       <c r="E51">
-        <v>366.6560000000001</v>
+        <v>381.2</v>
       </c>
       <c r="F51">
-        <v>712.6560000000001</v>
+        <v>727.2</v>
       </c>
       <c r="G51">
         <v>107.2</v>
@@ -5469,28 +5469,28 @@
         <v>116.1</v>
       </c>
       <c r="M51">
-        <v>54.01932480000001</v>
+        <v>55.12176000000001</v>
       </c>
       <c r="N51">
-        <v>62.0806752</v>
+        <v>60.97824</v>
       </c>
       <c r="O51">
-        <v>13.036941792</v>
+        <v>12.8054304</v>
       </c>
       <c r="P51">
-        <v>49.043733408</v>
+        <v>48.1728096</v>
       </c>
       <c r="Q51">
-        <v>111.843733408</v>
+        <v>110.9728096</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1101636966027756</v>
+        <v>0.1112972897432548</v>
       </c>
       <c r="T51">
-        <v>1.085264391000165</v>
+        <v>1.104378399893045</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.149230861915549</v>
+        <v>2.106246244677238</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0855896448716274</v>
+        <v>0.08565362447583923</v>
       </c>
       <c r="C52">
-        <v>645.2607035896333</v>
+        <v>629.4733448411774</v>
       </c>
       <c r="D52">
-        <v>1265.260703589633</v>
+        <v>1264.017344841177</v>
       </c>
       <c r="E52">
-        <v>381.2</v>
+        <v>395.744</v>
       </c>
       <c r="F52">
-        <v>727.2</v>
+        <v>741.744</v>
       </c>
       <c r="G52">
         <v>107.2</v>
@@ -5551,28 +5551,28 @@
         <v>116.1</v>
       </c>
       <c r="M52">
-        <v>55.12176000000001</v>
+        <v>56.2241952</v>
       </c>
       <c r="N52">
-        <v>60.97824</v>
+        <v>59.8758048</v>
       </c>
       <c r="O52">
-        <v>12.8054304</v>
+        <v>12.573919008</v>
       </c>
       <c r="P52">
-        <v>48.1728096</v>
+        <v>47.30188579200001</v>
       </c>
       <c r="Q52">
-        <v>110.9728096</v>
+        <v>110.101885792</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1112972897432548</v>
+        <v>0.1124771519915086</v>
       </c>
       <c r="T52">
-        <v>1.104378399893045</v>
+        <v>1.124272572414206</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.106246244677238</v>
+        <v>2.064947298703175</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08565362447583923</v>
+        <v>0.08571760408005105</v>
       </c>
       <c r="C53">
-        <v>629.4733448411774</v>
+        <v>613.68842736555</v>
       </c>
       <c r="D53">
-        <v>1264.017344841177</v>
+        <v>1262.77642736555</v>
       </c>
       <c r="E53">
-        <v>395.744</v>
+        <v>410.2880000000001</v>
       </c>
       <c r="F53">
-        <v>741.744</v>
+        <v>756.2880000000001</v>
       </c>
       <c r="G53">
         <v>107.2</v>
@@ -5633,28 +5633,28 @@
         <v>116.1</v>
       </c>
       <c r="M53">
-        <v>56.2241952</v>
+        <v>57.32663040000001</v>
       </c>
       <c r="N53">
-        <v>59.8758048</v>
+        <v>58.7733696</v>
       </c>
       <c r="O53">
-        <v>12.573919008</v>
+        <v>12.342407616</v>
       </c>
       <c r="P53">
-        <v>47.30188579200001</v>
+        <v>46.43096198399999</v>
       </c>
       <c r="Q53">
-        <v>110.101885792</v>
+        <v>109.230961984</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1124771519915086</v>
+        <v>0.113706175166773</v>
       </c>
       <c r="T53">
-        <v>1.124272572414206</v>
+        <v>1.144995668790415</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.064947298703175</v>
+        <v>2.025236773728113</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08571760408005105</v>
+        <v>0.09172712368426286</v>
       </c>
       <c r="C54">
-        <v>613.68842736555</v>
+        <v>492.5320707222618</v>
       </c>
       <c r="D54">
-        <v>1262.77642736555</v>
+        <v>1156.164070722262</v>
       </c>
       <c r="E54">
-        <v>410.2880000000001</v>
+        <v>424.8320000000001</v>
       </c>
       <c r="F54">
-        <v>756.2880000000001</v>
+        <v>770.8320000000001</v>
       </c>
       <c r="G54">
         <v>107.2</v>
@@ -5715,45 +5715,45 @@
         <v>116.1</v>
       </c>
       <c r="M54">
-        <v>57.32663040000001</v>
+        <v>69.37488</v>
       </c>
       <c r="N54">
-        <v>58.7733696</v>
+        <v>46.72512</v>
       </c>
       <c r="O54">
-        <v>12.342407616</v>
+        <v>9.8122752</v>
       </c>
       <c r="P54">
-        <v>46.43096198399999</v>
+        <v>36.9128448</v>
       </c>
       <c r="Q54">
-        <v>109.230961984</v>
+        <v>99.7128448</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.113706175166773</v>
+        <v>0.1149874972005593</v>
       </c>
       <c r="T54">
-        <v>1.144995668790415</v>
+        <v>1.166600599054973</v>
       </c>
       <c r="U54">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V54">
         <v>0.21</v>
       </c>
       <c r="W54">
-        <v>0.059882</v>
+        <v>0.0711</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.025236773728113</v>
+        <v>1.673516408244598</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09172712368426286</v>
+        <v>0.09190328328847468</v>
       </c>
       <c r="C55">
-        <v>492.5320707222618</v>
+        <v>475.1338100537356</v>
       </c>
       <c r="D55">
-        <v>1156.164070722262</v>
+        <v>1153.309810053736</v>
       </c>
       <c r="E55">
-        <v>424.8320000000001</v>
+        <v>439.3760000000001</v>
       </c>
       <c r="F55">
-        <v>770.8320000000001</v>
+        <v>785.3760000000001</v>
       </c>
       <c r="G55">
         <v>107.2</v>
@@ -5797,28 +5797,28 @@
         <v>116.1</v>
       </c>
       <c r="M55">
-        <v>69.37488</v>
+        <v>70.68384</v>
       </c>
       <c r="N55">
-        <v>46.72512</v>
+        <v>45.41616</v>
       </c>
       <c r="O55">
-        <v>9.8122752</v>
+        <v>9.537393600000001</v>
       </c>
       <c r="P55">
-        <v>36.9128448</v>
+        <v>35.8787664</v>
       </c>
       <c r="Q55">
-        <v>99.7128448</v>
+        <v>98.6787664</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1149874972005593</v>
+        <v>0.1163245288879884</v>
       </c>
       <c r="T55">
-        <v>1.166600599054973</v>
+        <v>1.189144874113643</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.673516408244598</v>
+        <v>1.642525363647476</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09190328328847468</v>
+        <v>0.09207944289268652</v>
       </c>
       <c r="C56">
-        <v>475.1338100537356</v>
+        <v>457.7496074958415</v>
       </c>
       <c r="D56">
-        <v>1153.309810053736</v>
+        <v>1150.469607495842</v>
       </c>
       <c r="E56">
-        <v>439.3760000000001</v>
+        <v>453.9200000000001</v>
       </c>
       <c r="F56">
-        <v>785.3760000000001</v>
+        <v>799.9200000000001</v>
       </c>
       <c r="G56">
         <v>107.2</v>
@@ -5879,28 +5879,28 @@
         <v>116.1</v>
       </c>
       <c r="M56">
-        <v>70.68384</v>
+        <v>71.9928</v>
       </c>
       <c r="N56">
-        <v>45.41616</v>
+        <v>44.10720000000001</v>
       </c>
       <c r="O56">
-        <v>9.537393600000001</v>
+        <v>9.262512000000001</v>
       </c>
       <c r="P56">
-        <v>35.8787664</v>
+        <v>34.844688</v>
       </c>
       <c r="Q56">
-        <v>98.6787664</v>
+        <v>97.644688</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1163245288879884</v>
+        <v>0.11772098420597</v>
       </c>
       <c r="T56">
-        <v>1.189144874113643</v>
+        <v>1.212691116952698</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.642525363647476</v>
+        <v>1.612661266126613</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09207944289268652</v>
+        <v>0.09225560249689835</v>
       </c>
       <c r="C57">
-        <v>457.7496074958415</v>
+        <v>440.3793594429546</v>
       </c>
       <c r="D57">
-        <v>1150.469607495842</v>
+        <v>1147.643359442955</v>
       </c>
       <c r="E57">
-        <v>453.9200000000001</v>
+        <v>468.4640000000002</v>
       </c>
       <c r="F57">
-        <v>799.9200000000001</v>
+        <v>814.4640000000002</v>
       </c>
       <c r="G57">
         <v>107.2</v>
@@ -5961,28 +5961,28 @@
         <v>116.1</v>
       </c>
       <c r="M57">
-        <v>71.9928</v>
+        <v>73.30176000000002</v>
       </c>
       <c r="N57">
-        <v>44.10720000000001</v>
+        <v>42.79823999999999</v>
       </c>
       <c r="O57">
-        <v>9.262512000000001</v>
+        <v>8.987630399999999</v>
       </c>
       <c r="P57">
-        <v>34.844688</v>
+        <v>33.81060959999999</v>
       </c>
       <c r="Q57">
-        <v>97.644688</v>
+        <v>96.61060959999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.11772098420597</v>
+        <v>0.119180914765678</v>
       </c>
       <c r="T57">
-        <v>1.212691116952698</v>
+        <v>1.237307643557164</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.612661266126613</v>
+        <v>1.583863743517209</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09225560249689835</v>
+        <v>0.09243176210111018</v>
       </c>
       <c r="C58">
-        <v>440.3793594429546</v>
+        <v>423.0229633050259</v>
       </c>
       <c r="D58">
-        <v>1147.643359442955</v>
+        <v>1144.830963305026</v>
       </c>
       <c r="E58">
-        <v>468.4640000000002</v>
+        <v>483.0080000000002</v>
       </c>
       <c r="F58">
-        <v>814.4640000000002</v>
+        <v>829.0080000000002</v>
       </c>
       <c r="G58">
         <v>107.2</v>
@@ -6043,28 +6043,28 @@
         <v>116.1</v>
       </c>
       <c r="M58">
-        <v>73.30176000000002</v>
+        <v>74.61072000000001</v>
       </c>
       <c r="N58">
-        <v>42.79823999999999</v>
+        <v>41.48927999999999</v>
       </c>
       <c r="O58">
-        <v>8.987630399999999</v>
+        <v>8.712748799999998</v>
       </c>
       <c r="P58">
-        <v>33.81060959999999</v>
+        <v>32.77653119999999</v>
       </c>
       <c r="Q58">
-        <v>96.61060959999999</v>
+        <v>95.57653119999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.119180914765678</v>
+        <v>0.1207087490723492</v>
       </c>
       <c r="T58">
-        <v>1.237307643557164</v>
+        <v>1.26306912488742</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.583863743517209</v>
+        <v>1.556076660297609</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09243176210111018</v>
+        <v>0.09260792170532198</v>
       </c>
       <c r="C59">
-        <v>423.0229633050259</v>
+        <v>405.6803174951713</v>
       </c>
       <c r="D59">
-        <v>1144.830963305026</v>
+        <v>1142.032317495171</v>
       </c>
       <c r="E59">
-        <v>483.0080000000002</v>
+        <v>497.5520000000001</v>
       </c>
       <c r="F59">
-        <v>829.0080000000002</v>
+        <v>843.5520000000001</v>
       </c>
       <c r="G59">
         <v>107.2</v>
@@ -6125,28 +6125,28 @@
         <v>116.1</v>
       </c>
       <c r="M59">
-        <v>74.61072000000001</v>
+        <v>75.91968000000001</v>
       </c>
       <c r="N59">
-        <v>41.48927999999999</v>
+        <v>40.18031999999999</v>
       </c>
       <c r="O59">
-        <v>8.712748799999998</v>
+        <v>8.437867199999999</v>
       </c>
       <c r="P59">
-        <v>32.77653119999999</v>
+        <v>31.7424528</v>
       </c>
       <c r="Q59">
-        <v>95.57653119999999</v>
+        <v>94.54245279999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1207087490723492</v>
+        <v>0.1223093373936238</v>
       </c>
       <c r="T59">
-        <v>1.26306912488742</v>
+        <v>1.290057343423879</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.556076660297609</v>
+        <v>1.529247752361443</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09260792170532199</v>
+        <v>0.09278408130953381</v>
       </c>
       <c r="C60">
-        <v>405.6803174951712</v>
+        <v>388.3513214174368</v>
       </c>
       <c r="D60">
-        <v>1142.032317495171</v>
+        <v>1139.247321417437</v>
       </c>
       <c r="E60">
-        <v>497.552</v>
+        <v>512.096</v>
       </c>
       <c r="F60">
-        <v>843.552</v>
+        <v>858.096</v>
       </c>
       <c r="G60">
         <v>107.2</v>
@@ -6207,28 +6207,28 @@
         <v>116.1</v>
       </c>
       <c r="M60">
-        <v>75.91968</v>
+        <v>77.22864</v>
       </c>
       <c r="N60">
-        <v>40.18032000000001</v>
+        <v>38.87136000000001</v>
       </c>
       <c r="O60">
-        <v>8.437867200000001</v>
+        <v>8.162985600000003</v>
       </c>
       <c r="P60">
-        <v>31.74245280000001</v>
+        <v>30.70837440000001</v>
       </c>
       <c r="Q60">
-        <v>94.54245280000001</v>
+        <v>93.50837440000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1223093373936238</v>
+        <v>0.1239880031939849</v>
       </c>
       <c r="T60">
-        <v>1.290057343423878</v>
+        <v>1.31836206042553</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.529247752361443</v>
+        <v>1.503328298931588</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09278408130953381</v>
+        <v>0.1220486327253375</v>
       </c>
       <c r="C61">
-        <v>388.3513214174368</v>
+        <v>45.3439843256898</v>
       </c>
       <c r="D61">
-        <v>1139.247321417437</v>
+        <v>810.7839843256897</v>
       </c>
       <c r="E61">
-        <v>512.096</v>
+        <v>526.64</v>
       </c>
       <c r="F61">
-        <v>858.096</v>
+        <v>872.64</v>
       </c>
       <c r="G61">
         <v>107.2</v>
@@ -6289,45 +6289,45 @@
         <v>116.1</v>
       </c>
       <c r="M61">
-        <v>77.22864</v>
+        <v>128.103552</v>
       </c>
       <c r="N61">
-        <v>38.87136000000001</v>
+        <v>-12.003552</v>
       </c>
       <c r="O61">
-        <v>8.162985600000003</v>
+        <v>-2.52074592</v>
       </c>
       <c r="P61">
-        <v>30.70837440000001</v>
+        <v>-9.48280608</v>
       </c>
       <c r="Q61">
-        <v>93.50837440000001</v>
+        <v>53.31719391999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1239880031939849</v>
+        <v>0.1268306164668092</v>
       </c>
       <c r="T61">
-        <v>1.31836206042553</v>
+        <v>1.366292603965</v>
       </c>
       <c r="U61">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.21</v>
+        <v>0.1903225915234575</v>
       </c>
       <c r="W61">
-        <v>0.0711</v>
+        <v>0.1188606435643564</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.503328298931588</v>
+        <v>0.9062980548736073</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1220486327253375</v>
+        <v>0.1230586327253375</v>
       </c>
       <c r="C62">
-        <v>45.3439843256898</v>
+        <v>22.81170163000752</v>
       </c>
       <c r="D62">
-        <v>810.7839843256897</v>
+        <v>802.7957016300076</v>
       </c>
       <c r="E62">
-        <v>526.64</v>
+        <v>541.1840000000001</v>
       </c>
       <c r="F62">
-        <v>872.64</v>
+        <v>887.1840000000001</v>
       </c>
       <c r="G62">
         <v>107.2</v>
@@ -6371,37 +6371,37 @@
         <v>116.1</v>
       </c>
       <c r="M62">
-        <v>128.103552</v>
+        <v>130.2386112</v>
       </c>
       <c r="N62">
-        <v>-12.003552</v>
+        <v>-14.13861120000003</v>
       </c>
       <c r="O62">
-        <v>-2.52074592</v>
+        <v>-2.969108352000006</v>
       </c>
       <c r="P62">
-        <v>-9.48280608</v>
+        <v>-11.16950284800002</v>
       </c>
       <c r="Q62">
-        <v>53.31719391999999</v>
+        <v>51.63049715199998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1268306164668092</v>
+        <v>0.1289083245813427</v>
       </c>
       <c r="T62">
-        <v>1.366292603965</v>
+        <v>1.401325747656411</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1903225915234575</v>
+        <v>0.1872025490394664</v>
       </c>
       <c r="W62">
-        <v>0.1188606435643564</v>
+        <v>0.1193186658010063</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.9062980548736073</v>
+        <v>0.8914407097117446</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1230586327253375</v>
+        <v>0.1240686327253375</v>
       </c>
       <c r="C63">
-        <v>22.81170163000752</v>
+        <v>0.4352929495956914</v>
       </c>
       <c r="D63">
-        <v>802.7957016300076</v>
+        <v>794.9632929495957</v>
       </c>
       <c r="E63">
-        <v>541.1840000000001</v>
+        <v>555.7280000000001</v>
       </c>
       <c r="F63">
-        <v>887.1840000000001</v>
+        <v>901.7280000000001</v>
       </c>
       <c r="G63">
         <v>107.2</v>
@@ -6453,37 +6453,37 @@
         <v>116.1</v>
       </c>
       <c r="M63">
-        <v>130.2386112</v>
+        <v>132.3736704</v>
       </c>
       <c r="N63">
-        <v>-14.13861120000003</v>
+        <v>-16.2736704</v>
       </c>
       <c r="O63">
-        <v>-2.969108352000006</v>
+        <v>-3.417470784</v>
       </c>
       <c r="P63">
-        <v>-11.16950284800002</v>
+        <v>-12.856199616</v>
       </c>
       <c r="Q63">
-        <v>51.63049715199998</v>
+        <v>49.943800384</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1289083245813427</v>
+        <v>0.131095385754536</v>
       </c>
       <c r="T63">
-        <v>1.401325747656411</v>
+        <v>1.43820274101579</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1872025490394664</v>
+        <v>0.184183153087217</v>
       </c>
       <c r="W63">
-        <v>0.1193186658010063</v>
+        <v>0.1197619131267966</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8914407097117446</v>
+        <v>0.8770626337486522</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1240686327253375</v>
+        <v>0.1250786327253375</v>
       </c>
       <c r="C64">
-        <v>0.4352929495956914</v>
+        <v>-21.78975994890675</v>
       </c>
       <c r="D64">
-        <v>794.9632929495957</v>
+        <v>787.2822400510933</v>
       </c>
       <c r="E64">
-        <v>555.7280000000001</v>
+        <v>570.272</v>
       </c>
       <c r="F64">
-        <v>901.7280000000001</v>
+        <v>916.272</v>
       </c>
       <c r="G64">
         <v>107.2</v>
@@ -6535,37 +6535,37 @@
         <v>116.1</v>
       </c>
       <c r="M64">
-        <v>132.3736704</v>
+        <v>134.5087296</v>
       </c>
       <c r="N64">
-        <v>-16.2736704</v>
+        <v>-18.4087296</v>
       </c>
       <c r="O64">
-        <v>-3.417470784</v>
+        <v>-3.865833216</v>
       </c>
       <c r="P64">
-        <v>-12.856199616</v>
+        <v>-14.542896384</v>
       </c>
       <c r="Q64">
-        <v>49.943800384</v>
+        <v>48.25710361599999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.131095385754536</v>
+        <v>0.1334006664506045</v>
       </c>
       <c r="T64">
-        <v>1.43820274101579</v>
+        <v>1.477073085367568</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.184183153087217</v>
+        <v>0.1812596109747215</v>
       </c>
       <c r="W64">
-        <v>0.1197619131267966</v>
+        <v>0.1201910891089109</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8770626337486522</v>
+        <v>0.8631410046415307</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1250786327253375</v>
+        <v>0.1260886327253375</v>
       </c>
       <c r="C65">
-        <v>-21.78975994890675</v>
+        <v>-43.86780234659454</v>
       </c>
       <c r="D65">
-        <v>787.2822400510933</v>
+        <v>779.7481976534054</v>
       </c>
       <c r="E65">
-        <v>570.272</v>
+        <v>584.816</v>
       </c>
       <c r="F65">
-        <v>916.272</v>
+        <v>930.816</v>
       </c>
       <c r="G65">
         <v>107.2</v>
@@ -6617,37 +6617,37 @@
         <v>116.1</v>
       </c>
       <c r="M65">
-        <v>134.5087296</v>
+        <v>136.6437888</v>
       </c>
       <c r="N65">
-        <v>-18.4087296</v>
+        <v>-20.5437888</v>
       </c>
       <c r="O65">
-        <v>-3.865833216</v>
+        <v>-4.314195648</v>
       </c>
       <c r="P65">
-        <v>-14.542896384</v>
+        <v>-16.229593152</v>
       </c>
       <c r="Q65">
-        <v>48.25710361599999</v>
+        <v>46.570406848</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1334006664506045</v>
+        <v>0.1358340182964546</v>
       </c>
       <c r="T65">
-        <v>1.477073085367568</v>
+        <v>1.518102893294445</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1812596109747215</v>
+        <v>0.1784274295532414</v>
       </c>
       <c r="W65">
-        <v>0.1201910891089109</v>
+        <v>0.1206068533415842</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8631410046415307</v>
+        <v>0.8496544264440068</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1260886327253375</v>
+        <v>0.1270986327253376</v>
       </c>
       <c r="C66">
-        <v>-43.86780234659454</v>
+        <v>-65.80301476934721</v>
       </c>
       <c r="D66">
-        <v>779.7481976534054</v>
+        <v>772.3569852306529</v>
       </c>
       <c r="E66">
-        <v>584.816</v>
+        <v>599.3600000000001</v>
       </c>
       <c r="F66">
-        <v>930.816</v>
+        <v>945.3600000000001</v>
       </c>
       <c r="G66">
         <v>107.2</v>
@@ -6699,37 +6699,37 @@
         <v>116.1</v>
       </c>
       <c r="M66">
-        <v>136.6437888</v>
+        <v>138.778848</v>
       </c>
       <c r="N66">
-        <v>-20.5437888</v>
+        <v>-22.67884800000003</v>
       </c>
       <c r="O66">
-        <v>-4.314195648</v>
+        <v>-4.762558080000006</v>
       </c>
       <c r="P66">
-        <v>-16.229593152</v>
+        <v>-17.91628992000003</v>
       </c>
       <c r="Q66">
-        <v>46.570406848</v>
+        <v>44.88371007999997</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1358340182964546</v>
+        <v>0.1384064188192105</v>
       </c>
       <c r="T66">
-        <v>1.518102893294445</v>
+        <v>1.561477261674286</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1784274295532414</v>
+        <v>0.1756823921754992</v>
       </c>
       <c r="W66">
-        <v>0.1206068533415842</v>
+        <v>0.1210098248286367</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8496544264440068</v>
+        <v>0.8365828198833296</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1270986327253376</v>
+        <v>0.1281086327253375</v>
       </c>
       <c r="C67">
-        <v>-65.80301476934721</v>
+        <v>-87.59942072305751</v>
       </c>
       <c r="D67">
-        <v>772.3569852306529</v>
+        <v>765.1045792769426</v>
       </c>
       <c r="E67">
-        <v>599.3600000000001</v>
+        <v>613.9040000000001</v>
       </c>
       <c r="F67">
-        <v>945.3600000000001</v>
+        <v>959.9040000000001</v>
       </c>
       <c r="G67">
         <v>107.2</v>
@@ -6781,37 +6781,37 @@
         <v>116.1</v>
       </c>
       <c r="M67">
-        <v>138.778848</v>
+        <v>140.9139072</v>
       </c>
       <c r="N67">
-        <v>-22.67884800000003</v>
+        <v>-24.81390720000003</v>
       </c>
       <c r="O67">
-        <v>-4.762558080000006</v>
+        <v>-5.210920512000007</v>
       </c>
       <c r="P67">
-        <v>-17.91628992000003</v>
+        <v>-19.60298668800002</v>
       </c>
       <c r="Q67">
-        <v>44.88371007999997</v>
+        <v>43.19701331199997</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1384064188192105</v>
+        <v>0.1411301370197755</v>
       </c>
       <c r="T67">
-        <v>1.561477261674286</v>
+        <v>1.607403063488236</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1756823921754992</v>
+        <v>0.1730205377485977</v>
       </c>
       <c r="W67">
-        <v>0.1210098248286367</v>
+        <v>0.1214005850585059</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8365828198833296</v>
+        <v>0.8239073226123701</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1281086327253375</v>
+        <v>0.1291186327253376</v>
       </c>
       <c r="C68">
-        <v>-87.59942072305751</v>
+        <v>-109.2608939971153</v>
       </c>
       <c r="D68">
-        <v>765.1045792769426</v>
+        <v>757.9871060028847</v>
       </c>
       <c r="E68">
-        <v>613.9040000000001</v>
+        <v>628.4480000000001</v>
       </c>
       <c r="F68">
-        <v>959.9040000000001</v>
+        <v>974.4480000000001</v>
       </c>
       <c r="G68">
         <v>107.2</v>
@@ -6863,37 +6863,37 @@
         <v>116.1</v>
       </c>
       <c r="M68">
-        <v>140.9139072</v>
+        <v>143.0489664</v>
       </c>
       <c r="N68">
-        <v>-24.81390720000003</v>
+        <v>-26.94896640000003</v>
       </c>
       <c r="O68">
-        <v>-5.210920512000007</v>
+        <v>-5.659282944000006</v>
       </c>
       <c r="P68">
-        <v>-19.60298668800002</v>
+        <v>-21.28968345600003</v>
       </c>
       <c r="Q68">
-        <v>43.19701331199997</v>
+        <v>41.51031654399997</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1411301370197755</v>
+        <v>0.1440189290506778</v>
       </c>
       <c r="T68">
-        <v>1.607403063488236</v>
+        <v>1.656112247230304</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1730205377485977</v>
+        <v>0.1704381416627977</v>
       </c>
       <c r="W68">
-        <v>0.1214005850585059</v>
+        <v>0.1217796808039013</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8239073226123701</v>
+        <v>0.811610198394275</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1291186327253376</v>
+        <v>0.1679723108927323</v>
       </c>
       <c r="C69">
-        <v>-109.2608939971153</v>
+        <v>-323.5710592155028</v>
       </c>
       <c r="D69">
-        <v>757.9871060028847</v>
+        <v>558.2209407844973</v>
       </c>
       <c r="E69">
-        <v>628.4480000000001</v>
+        <v>642.9920000000002</v>
       </c>
       <c r="F69">
-        <v>974.4480000000001</v>
+        <v>988.9920000000002</v>
       </c>
       <c r="G69">
         <v>107.2</v>
@@ -6945,45 +6945,45 @@
         <v>116.1</v>
       </c>
       <c r="M69">
-        <v>143.0489664</v>
+        <v>198.5895936000001</v>
       </c>
       <c r="N69">
-        <v>-26.94896640000003</v>
+        <v>-82.48959360000005</v>
       </c>
       <c r="O69">
-        <v>-5.659282944000006</v>
+        <v>-17.32281465600001</v>
       </c>
       <c r="P69">
-        <v>-21.28968345600003</v>
+        <v>-65.16677894400004</v>
       </c>
       <c r="Q69">
-        <v>41.51031654399997</v>
+        <v>-2.366778944000046</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1440189290506778</v>
+        <v>0.1505997648566202</v>
       </c>
       <c r="T69">
-        <v>1.656112247230304</v>
+        <v>1.767074593089417</v>
       </c>
       <c r="U69">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1704381416627977</v>
+        <v>0.1227707834938638</v>
       </c>
       <c r="W69">
-        <v>0.1217796808039013</v>
+        <v>0.1761476266744322</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.811610198394275</v>
+        <v>0.5846227785422085</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1679723108927323</v>
+        <v>0.1695223108927323</v>
       </c>
       <c r="C70">
-        <v>-323.5710592155028</v>
+        <v>-343.9230183295181</v>
       </c>
       <c r="D70">
-        <v>558.2209407844973</v>
+        <v>552.4129816704821</v>
       </c>
       <c r="E70">
-        <v>642.9920000000002</v>
+        <v>657.5360000000002</v>
       </c>
       <c r="F70">
-        <v>988.9920000000002</v>
+        <v>1003.536</v>
       </c>
       <c r="G70">
         <v>107.2</v>
@@ -7027,37 +7027,37 @@
         <v>116.1</v>
       </c>
       <c r="M70">
-        <v>198.5895936000001</v>
+        <v>201.5100288</v>
       </c>
       <c r="N70">
-        <v>-82.48959360000005</v>
+        <v>-85.41002880000003</v>
       </c>
       <c r="O70">
-        <v>-17.32281465600001</v>
+        <v>-17.93610604800001</v>
       </c>
       <c r="P70">
-        <v>-65.16677894400004</v>
+        <v>-67.47392275200002</v>
       </c>
       <c r="Q70">
-        <v>-2.366778944000046</v>
+        <v>-4.673922752000024</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1505997648566202</v>
+        <v>0.1539804024326402</v>
       </c>
       <c r="T70">
-        <v>1.767074593089417</v>
+        <v>1.824076999318108</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1227707834938638</v>
+        <v>0.1209914967765614</v>
       </c>
       <c r="W70">
-        <v>0.1761476266744322</v>
+        <v>0.1765049074472665</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5846227785422085</v>
+        <v>0.5761499846502924</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1695223108927323</v>
+        <v>0.1710723108927323</v>
       </c>
       <c r="C71">
-        <v>-343.9230183295181</v>
+        <v>-364.1553651716225</v>
       </c>
       <c r="D71">
-        <v>552.4129816704821</v>
+        <v>546.7246348283776</v>
       </c>
       <c r="E71">
-        <v>657.5360000000002</v>
+        <v>672.0800000000002</v>
       </c>
       <c r="F71">
-        <v>1003.536</v>
+        <v>1018.08</v>
       </c>
       <c r="G71">
         <v>107.2</v>
@@ -7109,37 +7109,37 @@
         <v>116.1</v>
       </c>
       <c r="M71">
-        <v>201.5100288</v>
+        <v>204.430464</v>
       </c>
       <c r="N71">
-        <v>-85.41002880000003</v>
+        <v>-88.33046400000002</v>
       </c>
       <c r="O71">
-        <v>-17.93610604800001</v>
+        <v>-18.54939744</v>
       </c>
       <c r="P71">
-        <v>-67.47392275200002</v>
+        <v>-69.78106656000001</v>
       </c>
       <c r="Q71">
-        <v>-4.673922752000024</v>
+        <v>-6.981066560000016</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1539804024326402</v>
+        <v>0.1575864158470616</v>
       </c>
       <c r="T71">
-        <v>1.824076999318108</v>
+        <v>1.884879565962045</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1209914967765614</v>
+        <v>0.1192630468226105</v>
       </c>
       <c r="W71">
-        <v>0.1765049074472665</v>
+        <v>0.1768519801980198</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5761499846502924</v>
+        <v>0.5679192705838597</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1710723108927323</v>
+        <v>0.1726223108927324</v>
       </c>
       <c r="C72">
-        <v>-364.1553651716225</v>
+        <v>-384.2717571211551</v>
       </c>
       <c r="D72">
-        <v>546.7246348283776</v>
+        <v>541.1522428788451</v>
       </c>
       <c r="E72">
-        <v>672.0800000000002</v>
+        <v>686.6240000000003</v>
       </c>
       <c r="F72">
-        <v>1018.08</v>
+        <v>1032.624</v>
       </c>
       <c r="G72">
         <v>107.2</v>
@@ -7191,37 +7191,37 @@
         <v>116.1</v>
       </c>
       <c r="M72">
-        <v>204.430464</v>
+        <v>207.3508992</v>
       </c>
       <c r="N72">
-        <v>-88.33046400000002</v>
+        <v>-91.25089920000003</v>
       </c>
       <c r="O72">
-        <v>-18.54939744</v>
+        <v>-19.16268883200001</v>
       </c>
       <c r="P72">
-        <v>-69.78106656000001</v>
+        <v>-72.08821036800003</v>
       </c>
       <c r="Q72">
-        <v>-6.981066560000016</v>
+        <v>-9.288210368000037</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1575864158470616</v>
+        <v>0.1614411198417879</v>
       </c>
       <c r="T72">
-        <v>1.884879565962045</v>
+        <v>1.949875413064184</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1192630468226105</v>
+        <v>0.1175832855997569</v>
       </c>
       <c r="W72">
-        <v>0.1768519801980198</v>
+        <v>0.1771892762515688</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5679192705838597</v>
+        <v>0.5599204076178899</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1726223108927323</v>
+        <v>0.1741723108927324</v>
       </c>
       <c r="C73">
-        <v>-384.2717571211546</v>
+        <v>-404.2757039531735</v>
       </c>
       <c r="D73">
-        <v>541.1522428788454</v>
+        <v>535.6922960468265</v>
       </c>
       <c r="E73">
-        <v>686.624</v>
+        <v>701.1680000000001</v>
       </c>
       <c r="F73">
-        <v>1032.624</v>
+        <v>1047.168</v>
       </c>
       <c r="G73">
         <v>107.2</v>
@@ -7273,37 +7273,37 @@
         <v>116.1</v>
       </c>
       <c r="M73">
-        <v>207.3508992</v>
+        <v>210.2713344</v>
       </c>
       <c r="N73">
-        <v>-91.25089920000001</v>
+        <v>-94.17133440000002</v>
       </c>
       <c r="O73">
-        <v>-19.162688832</v>
+        <v>-19.775980224</v>
       </c>
       <c r="P73">
-        <v>-72.08821036800001</v>
+        <v>-74.39535417600001</v>
       </c>
       <c r="Q73">
-        <v>-9.288210368000009</v>
+        <v>-11.59535417600001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1614411198417879</v>
+        <v>0.1655711598361374</v>
       </c>
       <c r="T73">
-        <v>1.949875413064184</v>
+        <v>2.019513820673619</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1175832855997569</v>
+        <v>0.1159501844108713</v>
       </c>
       <c r="W73">
-        <v>0.1771892762515688</v>
+        <v>0.177517202970297</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5599204076178899</v>
+        <v>0.5521437352898636</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1741723108927324</v>
+        <v>0.1757223108927324</v>
       </c>
       <c r="C74">
-        <v>-404.2757039531735</v>
+        <v>-424.1705752103344</v>
       </c>
       <c r="D74">
-        <v>535.6922960468265</v>
+        <v>530.3414247896656</v>
       </c>
       <c r="E74">
-        <v>701.1680000000001</v>
+        <v>715.712</v>
       </c>
       <c r="F74">
-        <v>1047.168</v>
+        <v>1061.712</v>
       </c>
       <c r="G74">
         <v>107.2</v>
@@ -7355,37 +7355,37 @@
         <v>116.1</v>
       </c>
       <c r="M74">
-        <v>210.2713344</v>
+        <v>213.1917696</v>
       </c>
       <c r="N74">
-        <v>-94.17133440000002</v>
+        <v>-97.09176960000001</v>
       </c>
       <c r="O74">
-        <v>-19.775980224</v>
+        <v>-20.389271616</v>
       </c>
       <c r="P74">
-        <v>-74.39535417600001</v>
+        <v>-76.702497984</v>
       </c>
       <c r="Q74">
-        <v>-11.59535417600001</v>
+        <v>-13.90249798400001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1655711598361374</v>
+        <v>0.1700071287189573</v>
       </c>
       <c r="T74">
-        <v>2.019513820673619</v>
+        <v>2.094310628846716</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1159501844108713</v>
+        <v>0.1143618257203115</v>
       </c>
       <c r="W74">
-        <v>0.177517202970297</v>
+        <v>0.1778361453953615</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5521437352898636</v>
+        <v>0.5445801224776737</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1757223108927324</v>
+        <v>0.1772723108927323</v>
       </c>
       <c r="C75">
-        <v>-424.1705752103344</v>
+        <v>-443.9596071373236</v>
       </c>
       <c r="D75">
-        <v>530.3414247896656</v>
+        <v>525.0963928626765</v>
       </c>
       <c r="E75">
-        <v>715.712</v>
+        <v>730.2560000000001</v>
       </c>
       <c r="F75">
-        <v>1061.712</v>
+        <v>1076.256</v>
       </c>
       <c r="G75">
         <v>107.2</v>
@@ -7437,37 +7437,37 @@
         <v>116.1</v>
       </c>
       <c r="M75">
-        <v>213.1917696</v>
+        <v>216.1122048</v>
       </c>
       <c r="N75">
-        <v>-97.09176960000001</v>
+        <v>-100.0122048</v>
       </c>
       <c r="O75">
-        <v>-20.389271616</v>
+        <v>-21.002563008</v>
       </c>
       <c r="P75">
-        <v>-76.702497984</v>
+        <v>-79.00964179200002</v>
       </c>
       <c r="Q75">
-        <v>-13.90249798400001</v>
+        <v>-16.20964179200003</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1700071287189573</v>
+        <v>0.1747843259773788</v>
       </c>
       <c r="T75">
-        <v>2.094310628846716</v>
+        <v>2.174861037648513</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1143618257203115</v>
+        <v>0.11281639564301</v>
       </c>
       <c r="W75">
-        <v>0.1778361453953615</v>
+        <v>0.1781464677548836</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5445801224776737</v>
+        <v>0.5372209316333808</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1772723108927323</v>
+        <v>0.1788223108927323</v>
       </c>
       <c r="C76">
-        <v>-443.9596071373236</v>
+        <v>-463.6459092078345</v>
       </c>
       <c r="D76">
-        <v>525.0963928626765</v>
+        <v>519.9540907921656</v>
       </c>
       <c r="E76">
-        <v>730.2560000000001</v>
+        <v>744.8000000000002</v>
       </c>
       <c r="F76">
-        <v>1076.256</v>
+        <v>1090.8</v>
       </c>
       <c r="G76">
         <v>107.2</v>
@@ -7519,37 +7519,37 @@
         <v>116.1</v>
       </c>
       <c r="M76">
-        <v>216.1122048</v>
+        <v>219.03264</v>
       </c>
       <c r="N76">
-        <v>-100.0122048</v>
+        <v>-102.93264</v>
       </c>
       <c r="O76">
-        <v>-21.002563008</v>
+        <v>-21.61585440000001</v>
       </c>
       <c r="P76">
-        <v>-79.00964179200002</v>
+        <v>-81.31678560000003</v>
       </c>
       <c r="Q76">
-        <v>-16.20964179200003</v>
+        <v>-18.51678560000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1747843259773788</v>
+        <v>0.1799436990164739</v>
       </c>
       <c r="T76">
-        <v>2.174861037648513</v>
+        <v>2.261855479154454</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.11281639564301</v>
+        <v>0.1113121770344365</v>
       </c>
       <c r="W76">
-        <v>0.1781464677548836</v>
+        <v>0.1784485148514852</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5372209316333808</v>
+        <v>0.530057985878269</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1788223108927323</v>
+        <v>0.1803723108927324</v>
       </c>
       <c r="C77">
-        <v>-463.6459092078345</v>
+        <v>-483.2324702717492</v>
       </c>
       <c r="D77">
-        <v>519.9540907921656</v>
+        <v>514.9115297282508</v>
       </c>
       <c r="E77">
-        <v>744.8000000000002</v>
+        <v>759.3440000000001</v>
       </c>
       <c r="F77">
-        <v>1090.8</v>
+        <v>1105.344</v>
       </c>
       <c r="G77">
         <v>107.2</v>
@@ -7601,37 +7601,37 @@
         <v>116.1</v>
       </c>
       <c r="M77">
-        <v>219.03264</v>
+        <v>221.9530752</v>
       </c>
       <c r="N77">
-        <v>-102.93264</v>
+        <v>-105.8530752</v>
       </c>
       <c r="O77">
-        <v>-21.61585440000001</v>
+        <v>-22.229145792</v>
       </c>
       <c r="P77">
-        <v>-81.31678560000003</v>
+        <v>-83.62392940800001</v>
       </c>
       <c r="Q77">
-        <v>-18.51678560000003</v>
+        <v>-20.82392940800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1799436990164739</v>
+        <v>0.185533019808827</v>
       </c>
       <c r="T77">
-        <v>2.261855479154454</v>
+        <v>2.356099457452556</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1113121770344365</v>
+        <v>0.1098475431260886</v>
       </c>
       <c r="W77">
-        <v>0.1784485148514852</v>
+        <v>0.1787426133402814</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.530057985878269</v>
+        <v>0.5230835386956603</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1803723108927324</v>
+        <v>0.1819223108927323</v>
       </c>
       <c r="C78">
-        <v>-483.2324702717492</v>
+        <v>-502.7221643480618</v>
       </c>
       <c r="D78">
-        <v>514.9115297282508</v>
+        <v>509.9658356519383</v>
       </c>
       <c r="E78">
-        <v>759.3440000000001</v>
+        <v>773.8880000000001</v>
       </c>
       <c r="F78">
-        <v>1105.344</v>
+        <v>1119.888</v>
       </c>
       <c r="G78">
         <v>107.2</v>
@@ -7683,37 +7683,37 @@
         <v>116.1</v>
       </c>
       <c r="M78">
-        <v>221.9530752</v>
+        <v>224.8735104</v>
       </c>
       <c r="N78">
-        <v>-105.8530752</v>
+        <v>-108.7735104</v>
       </c>
       <c r="O78">
-        <v>-22.229145792</v>
+        <v>-22.842437184</v>
       </c>
       <c r="P78">
-        <v>-83.62392940800001</v>
+        <v>-85.93107321600003</v>
       </c>
       <c r="Q78">
-        <v>-20.82392940800001</v>
+        <v>-23.13107321600003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.185533019808827</v>
+        <v>0.1916083684961673</v>
       </c>
       <c r="T78">
-        <v>2.356099457452556</v>
+        <v>2.458538564298319</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1098475431260886</v>
+        <v>0.1084209516569187</v>
       </c>
       <c r="W78">
-        <v>0.1787426133402814</v>
+        <v>0.1790290729072907</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5230835386956603</v>
+        <v>0.5162902459853269</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1819223108927323</v>
+        <v>0.1834723108927324</v>
       </c>
       <c r="C79">
-        <v>-502.7221643480618</v>
+        <v>-522.1177560871307</v>
       </c>
       <c r="D79">
-        <v>509.9658356519383</v>
+        <v>505.1142439128693</v>
       </c>
       <c r="E79">
-        <v>773.8880000000001</v>
+        <v>788.432</v>
       </c>
       <c r="F79">
-        <v>1119.888</v>
+        <v>1134.432</v>
       </c>
       <c r="G79">
         <v>107.2</v>
@@ -7765,37 +7765,37 @@
         <v>116.1</v>
       </c>
       <c r="M79">
-        <v>224.8735104</v>
+        <v>227.7939456</v>
       </c>
       <c r="N79">
-        <v>-108.7735104</v>
+        <v>-111.6939456</v>
       </c>
       <c r="O79">
-        <v>-22.842437184</v>
+        <v>-23.455728576</v>
       </c>
       <c r="P79">
-        <v>-85.93107321600003</v>
+        <v>-88.23821702399999</v>
       </c>
       <c r="Q79">
-        <v>-23.13107321600003</v>
+        <v>-25.438217024</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1916083684961673</v>
+        <v>0.1982360216096294</v>
       </c>
       <c r="T79">
-        <v>2.458538564298319</v>
+        <v>2.57029031722097</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1084209516569187</v>
+        <v>0.107030939456189</v>
       </c>
       <c r="W79">
-        <v>0.1790290729072907</v>
+        <v>0.1793081873571973</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5162902459853269</v>
+        <v>0.5096711402675664</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1834723108927324</v>
+        <v>0.1850223108927324</v>
       </c>
       <c r="C80">
-        <v>-522.1177560871307</v>
+        <v>-541.4219059240796</v>
       </c>
       <c r="D80">
-        <v>505.1142439128693</v>
+        <v>500.3540940759204</v>
       </c>
       <c r="E80">
-        <v>788.432</v>
+        <v>802.9760000000001</v>
       </c>
       <c r="F80">
-        <v>1134.432</v>
+        <v>1148.976</v>
       </c>
       <c r="G80">
         <v>107.2</v>
@@ -7847,37 +7847,37 @@
         <v>116.1</v>
       </c>
       <c r="M80">
-        <v>227.7939456</v>
+        <v>230.7143808</v>
       </c>
       <c r="N80">
-        <v>-111.6939456</v>
+        <v>-114.6143808</v>
       </c>
       <c r="O80">
-        <v>-23.455728576</v>
+        <v>-24.06901996800001</v>
       </c>
       <c r="P80">
-        <v>-88.23821702399999</v>
+        <v>-90.54536083200003</v>
       </c>
       <c r="Q80">
-        <v>-25.438217024</v>
+        <v>-27.74536083200003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1982360216096294</v>
+        <v>0.2054948797815166</v>
       </c>
       <c r="T80">
-        <v>2.57029031722097</v>
+        <v>2.692685094231493</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.107030939456189</v>
+        <v>0.1056761174377562</v>
       </c>
       <c r="W80">
-        <v>0.1793081873571973</v>
+        <v>0.1795802356184986</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5096711402675664</v>
+        <v>0.5032196068464579</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1850223108927324</v>
+        <v>0.2150257286058033</v>
       </c>
       <c r="C81">
-        <v>-541.4219059240796</v>
+        <v>-633.1585827111575</v>
       </c>
       <c r="D81">
-        <v>500.3540940759204</v>
+        <v>423.1614172888427</v>
       </c>
       <c r="E81">
-        <v>802.9760000000001</v>
+        <v>817.5200000000002</v>
       </c>
       <c r="F81">
-        <v>1148.976</v>
+        <v>1163.52</v>
       </c>
       <c r="G81">
         <v>107.2</v>
@@ -7929,45 +7929,45 @@
         <v>116.1</v>
       </c>
       <c r="M81">
-        <v>230.7143808</v>
+        <v>274.3580160000001</v>
       </c>
       <c r="N81">
-        <v>-114.6143808</v>
+        <v>-158.2580160000001</v>
       </c>
       <c r="O81">
-        <v>-24.06901996800001</v>
+        <v>-33.23418336000001</v>
       </c>
       <c r="P81">
-        <v>-90.54536083200003</v>
+        <v>-125.0238326400001</v>
       </c>
       <c r="Q81">
-        <v>-27.74536083200003</v>
+        <v>-62.22383264000005</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2054948797815166</v>
+        <v>0.2157467123359469</v>
       </c>
       <c r="T81">
-        <v>2.692685094231493</v>
+        <v>2.865545719103367</v>
       </c>
       <c r="U81">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1056761174377562</v>
+        <v>0.08886563751795025</v>
       </c>
       <c r="W81">
-        <v>0.1795802356184986</v>
+        <v>0.2148454826732673</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.5032196068464579</v>
+        <v>0.4231697024664298</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2150257286058033</v>
+        <v>0.2169257286058033</v>
       </c>
       <c r="C82">
-        <v>-633.1585827111575</v>
+        <v>-651.7967467703071</v>
       </c>
       <c r="D82">
-        <v>423.1614172888427</v>
+        <v>419.067253229693</v>
       </c>
       <c r="E82">
-        <v>817.5200000000002</v>
+        <v>832.0640000000001</v>
       </c>
       <c r="F82">
-        <v>1163.52</v>
+        <v>1178.064</v>
       </c>
       <c r="G82">
         <v>107.2</v>
@@ -8011,37 +8011,37 @@
         <v>116.1</v>
       </c>
       <c r="M82">
-        <v>274.3580160000001</v>
+        <v>277.7874912</v>
       </c>
       <c r="N82">
-        <v>-158.2580160000001</v>
+        <v>-161.6874912</v>
       </c>
       <c r="O82">
-        <v>-33.23418336000001</v>
+        <v>-33.954373152</v>
       </c>
       <c r="P82">
-        <v>-125.0238326400001</v>
+        <v>-127.733118048</v>
       </c>
       <c r="Q82">
-        <v>-62.22383264000005</v>
+        <v>-64.93311804800001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2157467123359469</v>
+        <v>0.2246912761431021</v>
       </c>
       <c r="T82">
-        <v>2.865545719103367</v>
+        <v>3.01636391484565</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08886563751795025</v>
+        <v>0.08776853088192618</v>
       </c>
       <c r="W82">
-        <v>0.2148454826732673</v>
+        <v>0.2151041804180418</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4231697024664298</v>
+        <v>0.4179453851520295</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2169257286058033</v>
+        <v>0.2188257286058033</v>
       </c>
       <c r="C83">
-        <v>-651.7967467703071</v>
+        <v>-670.3564464157662</v>
       </c>
       <c r="D83">
-        <v>419.067253229693</v>
+        <v>415.0515535842339</v>
       </c>
       <c r="E83">
-        <v>832.0640000000001</v>
+        <v>846.6080000000002</v>
       </c>
       <c r="F83">
-        <v>1178.064</v>
+        <v>1192.608</v>
       </c>
       <c r="G83">
         <v>107.2</v>
@@ -8093,37 +8093,37 @@
         <v>116.1</v>
       </c>
       <c r="M83">
-        <v>277.7874912</v>
+        <v>281.2169664</v>
       </c>
       <c r="N83">
-        <v>-161.6874912</v>
+        <v>-165.1169664</v>
       </c>
       <c r="O83">
-        <v>-33.954373152</v>
+        <v>-34.674562944</v>
       </c>
       <c r="P83">
-        <v>-127.733118048</v>
+        <v>-130.442403456</v>
       </c>
       <c r="Q83">
-        <v>-64.93311804800001</v>
+        <v>-67.64240345600003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2246912761431021</v>
+        <v>0.2346296803732744</v>
       </c>
       <c r="T83">
-        <v>3.01636391484565</v>
+        <v>3.18393968789263</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08776853088192618</v>
+        <v>0.08669818294434171</v>
       </c>
       <c r="W83">
-        <v>0.2151041804180418</v>
+        <v>0.2153565684617242</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4179453851520295</v>
+        <v>0.4128484902111511</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2188257286058033</v>
+        <v>0.2207257286058033</v>
       </c>
       <c r="C84">
-        <v>-670.3564464157662</v>
+        <v>-688.8399158868215</v>
       </c>
       <c r="D84">
-        <v>415.0515535842339</v>
+        <v>411.1120841131788</v>
       </c>
       <c r="E84">
-        <v>846.6080000000002</v>
+        <v>861.1520000000003</v>
       </c>
       <c r="F84">
-        <v>1192.608</v>
+        <v>1207.152</v>
       </c>
       <c r="G84">
         <v>107.2</v>
@@ -8175,37 +8175,37 @@
         <v>116.1</v>
       </c>
       <c r="M84">
-        <v>281.2169664</v>
+        <v>284.6464416000001</v>
       </c>
       <c r="N84">
-        <v>-165.1169664</v>
+        <v>-168.5464416</v>
       </c>
       <c r="O84">
-        <v>-34.674562944</v>
+        <v>-35.39475273600001</v>
       </c>
       <c r="P84">
-        <v>-130.442403456</v>
+        <v>-133.151688864</v>
       </c>
       <c r="Q84">
-        <v>-67.64240345600003</v>
+        <v>-70.35168886400002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2346296803732744</v>
+        <v>0.2457373086305259</v>
       </c>
       <c r="T84">
-        <v>3.18393968789263</v>
+        <v>3.371230257768668</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08669818294434171</v>
+        <v>0.08565362652332555</v>
       </c>
       <c r="W84">
-        <v>0.2153565684617242</v>
+        <v>0.2156028748657998</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4128484902111511</v>
+        <v>0.407874412015836</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2207257286058033</v>
+        <v>0.2226257286058033</v>
       </c>
       <c r="C85">
-        <v>-688.8399158868215</v>
+        <v>-707.2493053950162</v>
       </c>
       <c r="D85">
-        <v>411.1120841131788</v>
+        <v>407.2466946049839</v>
       </c>
       <c r="E85">
-        <v>861.1520000000003</v>
+        <v>875.6960000000001</v>
       </c>
       <c r="F85">
-        <v>1207.152</v>
+        <v>1221.696</v>
       </c>
       <c r="G85">
         <v>107.2</v>
@@ -8257,37 +8257,37 @@
         <v>116.1</v>
       </c>
       <c r="M85">
-        <v>284.6464416000001</v>
+        <v>288.0759168000001</v>
       </c>
       <c r="N85">
-        <v>-168.5464416</v>
+        <v>-171.9759168</v>
       </c>
       <c r="O85">
-        <v>-35.39475273600001</v>
+        <v>-36.11494252800001</v>
       </c>
       <c r="P85">
-        <v>-133.151688864</v>
+        <v>-135.860974272</v>
       </c>
       <c r="Q85">
-        <v>-70.35168886400002</v>
+        <v>-73.06097427200005</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2457373086305259</v>
+        <v>0.2582333904199338</v>
       </c>
       <c r="T85">
-        <v>3.371230257768668</v>
+        <v>3.58193214887921</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08565362652332555</v>
+        <v>0.08463394049328596</v>
       </c>
       <c r="W85">
-        <v>0.2156028748657998</v>
+        <v>0.2158433168316832</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.407874412015836</v>
+        <v>0.4030187642537427</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2226257286058032</v>
+        <v>0.2245257286058033</v>
       </c>
       <c r="C86">
-        <v>-707.249305395016</v>
+        <v>-725.5866850376165</v>
       </c>
       <c r="D86">
-        <v>407.2466946049841</v>
+        <v>403.4533149623836</v>
       </c>
       <c r="E86">
-        <v>875.6960000000001</v>
+        <v>890.24</v>
       </c>
       <c r="F86">
-        <v>1221.696</v>
+        <v>1236.24</v>
       </c>
       <c r="G86">
         <v>107.2</v>
@@ -8339,37 +8339,37 @@
         <v>116.1</v>
       </c>
       <c r="M86">
-        <v>288.0759168000001</v>
+        <v>291.505392</v>
       </c>
       <c r="N86">
-        <v>-171.9759168</v>
+        <v>-175.405392</v>
       </c>
       <c r="O86">
-        <v>-36.11494252800001</v>
+        <v>-36.83513232</v>
       </c>
       <c r="P86">
-        <v>-135.860974272</v>
+        <v>-138.57025968</v>
       </c>
       <c r="Q86">
-        <v>-73.06097427200005</v>
+        <v>-75.77025968</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2582333904199336</v>
+        <v>0.2723956164479292</v>
       </c>
       <c r="T86">
-        <v>3.581932148879208</v>
+        <v>3.820727625471155</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08463394049328596</v>
+        <v>0.0836382470757179</v>
       </c>
       <c r="W86">
-        <v>0.2158433168316832</v>
+        <v>0.2160781013395457</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4030187642537427</v>
+        <v>0.3982773670272282</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2245257286058033</v>
+        <v>0.2264257286058033</v>
       </c>
       <c r="C87">
-        <v>-725.5866850376165</v>
+        <v>-743.854048494378</v>
       </c>
       <c r="D87">
-        <v>403.4533149623836</v>
+        <v>399.7299515056221</v>
       </c>
       <c r="E87">
-        <v>890.24</v>
+        <v>904.7840000000001</v>
       </c>
       <c r="F87">
-        <v>1236.24</v>
+        <v>1250.784</v>
       </c>
       <c r="G87">
         <v>107.2</v>
@@ -8421,37 +8421,37 @@
         <v>116.1</v>
       </c>
       <c r="M87">
-        <v>291.505392</v>
+        <v>294.9348672</v>
       </c>
       <c r="N87">
-        <v>-175.405392</v>
+        <v>-178.8348672</v>
       </c>
       <c r="O87">
-        <v>-36.83513232</v>
+        <v>-37.55532211200001</v>
       </c>
       <c r="P87">
-        <v>-138.57025968</v>
+        <v>-141.279545088</v>
       </c>
       <c r="Q87">
-        <v>-75.77025968</v>
+        <v>-78.47954508800002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2723956164479292</v>
+        <v>0.2885810176227813</v>
       </c>
       <c r="T87">
-        <v>3.820727625471155</v>
+        <v>4.093636741576238</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0836382470757179</v>
+        <v>0.08266570931902349</v>
       </c>
       <c r="W87">
-        <v>0.2160781013395457</v>
+        <v>0.2163074257425743</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3982773670272282</v>
+        <v>0.3936462348524929</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2264257286058033</v>
+        <v>0.2283257286058032</v>
       </c>
       <c r="C88">
-        <v>-743.854048494378</v>
+        <v>-762.0533165214847</v>
       </c>
       <c r="D88">
-        <v>399.7299515056221</v>
+        <v>396.0746834785153</v>
       </c>
       <c r="E88">
-        <v>904.7840000000001</v>
+        <v>919.328</v>
       </c>
       <c r="F88">
-        <v>1250.784</v>
+        <v>1265.328</v>
       </c>
       <c r="G88">
         <v>107.2</v>
@@ -8503,37 +8503,37 @@
         <v>116.1</v>
       </c>
       <c r="M88">
-        <v>294.9348672</v>
+        <v>298.3643424</v>
       </c>
       <c r="N88">
-        <v>-178.8348672</v>
+        <v>-182.2643424</v>
       </c>
       <c r="O88">
-        <v>-37.55532211200001</v>
+        <v>-38.27551190399999</v>
       </c>
       <c r="P88">
-        <v>-141.279545088</v>
+        <v>-143.988830496</v>
       </c>
       <c r="Q88">
-        <v>-78.47954508800002</v>
+        <v>-81.18883049599999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2885810176227813</v>
+        <v>0.3072564805168413</v>
       </c>
       <c r="T88">
-        <v>4.093636741576238</v>
+        <v>4.40853187554364</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08266570931902349</v>
+        <v>0.08171552875213818</v>
       </c>
       <c r="W88">
-        <v>0.2163074257425743</v>
+        <v>0.2165314783202458</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3936462348524929</v>
+        <v>0.3891215654863723</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2283257286058032</v>
+        <v>0.2302257286058033</v>
       </c>
       <c r="C89">
-        <v>-762.0533165214847</v>
+        <v>-780.1863402555289</v>
       </c>
       <c r="D89">
-        <v>396.0746834785153</v>
+        <v>392.4856597444712</v>
       </c>
       <c r="E89">
-        <v>919.328</v>
+        <v>933.8720000000001</v>
       </c>
       <c r="F89">
-        <v>1265.328</v>
+        <v>1279.872</v>
       </c>
       <c r="G89">
         <v>107.2</v>
@@ -8585,37 +8585,37 @@
         <v>116.1</v>
       </c>
       <c r="M89">
-        <v>298.3643424</v>
+        <v>301.7938176</v>
       </c>
       <c r="N89">
-        <v>-182.2643424</v>
+        <v>-185.6938176</v>
       </c>
       <c r="O89">
-        <v>-38.27551190399999</v>
+        <v>-38.995701696</v>
       </c>
       <c r="P89">
-        <v>-143.988830496</v>
+        <v>-146.698115904</v>
       </c>
       <c r="Q89">
-        <v>-81.18883049599999</v>
+        <v>-83.89811590399999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3072564805168413</v>
+        <v>0.3290445205599116</v>
       </c>
       <c r="T89">
-        <v>4.40853187554364</v>
+        <v>4.775909531838945</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08171552875213818</v>
+        <v>0.0807869431981366</v>
       </c>
       <c r="W89">
-        <v>0.2165314783202458</v>
+        <v>0.2167504387938794</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3891215654863723</v>
+        <v>0.3846997295149363</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2302257286058033</v>
+        <v>0.2321257286058032</v>
       </c>
       <c r="C90">
-        <v>-780.1863402555289</v>
+        <v>-798.2549043394665</v>
       </c>
       <c r="D90">
-        <v>392.4856597444712</v>
+        <v>388.9610956605336</v>
       </c>
       <c r="E90">
-        <v>933.8720000000001</v>
+        <v>948.4160000000002</v>
       </c>
       <c r="F90">
-        <v>1279.872</v>
+        <v>1294.416</v>
       </c>
       <c r="G90">
         <v>107.2</v>
@@ -8667,37 +8667,37 @@
         <v>116.1</v>
       </c>
       <c r="M90">
-        <v>301.7938176</v>
+        <v>305.2232928</v>
       </c>
       <c r="N90">
-        <v>-185.6938176</v>
+        <v>-189.1232928</v>
       </c>
       <c r="O90">
-        <v>-38.995701696</v>
+        <v>-39.715891488</v>
       </c>
       <c r="P90">
-        <v>-146.698115904</v>
+        <v>-149.407401312</v>
       </c>
       <c r="Q90">
-        <v>-83.89811590399999</v>
+        <v>-86.60740131199999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3290445205599116</v>
+        <v>0.3547940224289944</v>
       </c>
       <c r="T90">
-        <v>4.775909531838945</v>
+        <v>5.210083125642486</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0807869431981366</v>
+        <v>0.07987922473523619</v>
       </c>
       <c r="W90">
-        <v>0.2167504387938794</v>
+        <v>0.2169644788074313</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3846997295149363</v>
+        <v>0.3803772606439819</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2321257286058032</v>
+        <v>0.2340257286058032</v>
       </c>
       <c r="C91">
-        <v>-798.2549043394665</v>
+        <v>-816.260729881648</v>
       </c>
       <c r="D91">
-        <v>388.9610956605336</v>
+        <v>385.4992701183521</v>
       </c>
       <c r="E91">
-        <v>948.4160000000002</v>
+        <v>962.96</v>
       </c>
       <c r="F91">
-        <v>1294.416</v>
+        <v>1308.96</v>
       </c>
       <c r="G91">
         <v>107.2</v>
@@ -8749,37 +8749,37 @@
         <v>116.1</v>
       </c>
       <c r="M91">
-        <v>305.2232928</v>
+        <v>308.652768</v>
       </c>
       <c r="N91">
-        <v>-189.1232928</v>
+        <v>-192.552768</v>
       </c>
       <c r="O91">
-        <v>-39.715891488</v>
+        <v>-40.43608128</v>
       </c>
       <c r="P91">
-        <v>-149.407401312</v>
+        <v>-152.11668672</v>
       </c>
       <c r="Q91">
-        <v>-86.60740131199999</v>
+        <v>-89.31668672000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3547940224289944</v>
+        <v>0.3856934246718938</v>
       </c>
       <c r="T91">
-        <v>5.210083125642486</v>
+        <v>5.731091438206733</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07987922473523619</v>
+        <v>0.07899167779373356</v>
       </c>
       <c r="W91">
-        <v>0.2169644788074313</v>
+        <v>0.2171737623762376</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3803772606439819</v>
+        <v>0.3761508466368265</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2340257286058032</v>
+        <v>0.2359257286058033</v>
       </c>
       <c r="C92">
-        <v>-816.260729881648</v>
+        <v>-834.2054772582231</v>
       </c>
       <c r="D92">
-        <v>385.4992701183521</v>
+        <v>382.098522741777</v>
       </c>
       <c r="E92">
-        <v>962.96</v>
+        <v>977.5040000000001</v>
       </c>
       <c r="F92">
-        <v>1308.96</v>
+        <v>1323.504</v>
       </c>
       <c r="G92">
         <v>107.2</v>
@@ -8831,37 +8831,37 @@
         <v>116.1</v>
       </c>
       <c r="M92">
-        <v>308.652768</v>
+        <v>312.0822432000001</v>
       </c>
       <c r="N92">
-        <v>-192.552768</v>
+        <v>-195.9822432</v>
       </c>
       <c r="O92">
-        <v>-40.43608128</v>
+        <v>-41.156271072</v>
       </c>
       <c r="P92">
-        <v>-152.11668672</v>
+        <v>-154.825972128</v>
       </c>
       <c r="Q92">
-        <v>-89.31668672000002</v>
+        <v>-92.02597212800002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3856934246718938</v>
+        <v>0.4234593607465488</v>
       </c>
       <c r="T92">
-        <v>5.731091438206733</v>
+        <v>6.367879375785261</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07899167779373356</v>
+        <v>0.07812363737841781</v>
       </c>
       <c r="W92">
-        <v>0.2171737623762376</v>
+        <v>0.2173784463061691</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3761508466368265</v>
+        <v>0.3720173208496087</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2359257286058033</v>
+        <v>0.2378257286058033</v>
       </c>
       <c r="C93">
-        <v>-834.2054772582231</v>
+        <v>-852.0907487685138</v>
       </c>
       <c r="D93">
-        <v>382.098522741777</v>
+        <v>378.7572512314865</v>
       </c>
       <c r="E93">
-        <v>977.5040000000001</v>
+        <v>992.0480000000002</v>
       </c>
       <c r="F93">
-        <v>1323.504</v>
+        <v>1338.048</v>
       </c>
       <c r="G93">
         <v>107.2</v>
@@ -8913,37 +8913,37 @@
         <v>116.1</v>
       </c>
       <c r="M93">
-        <v>312.0822432000001</v>
+        <v>315.5117184000001</v>
       </c>
       <c r="N93">
-        <v>-195.9822432</v>
+        <v>-199.4117184</v>
       </c>
       <c r="O93">
-        <v>-41.156271072</v>
+        <v>-41.87646086400001</v>
       </c>
       <c r="P93">
-        <v>-154.825972128</v>
+        <v>-157.535257536</v>
       </c>
       <c r="Q93">
-        <v>-92.02597212800002</v>
+        <v>-94.73525753600002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4234593607465488</v>
+        <v>0.4706667808398676</v>
       </c>
       <c r="T93">
-        <v>6.367879375785261</v>
+        <v>7.163864297758421</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07812363737841781</v>
+        <v>0.07727446740691327</v>
       </c>
       <c r="W93">
-        <v>0.2173784463061691</v>
+        <v>0.2175786805854499</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3720173208496087</v>
+        <v>0.3679736543186346</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2378257286058033</v>
+        <v>0.2397257286058033</v>
       </c>
       <c r="C94">
-        <v>-852.0907487685138</v>
+        <v>-869.918091152274</v>
       </c>
       <c r="D94">
-        <v>378.7572512314865</v>
+        <v>375.4739088477261</v>
       </c>
       <c r="E94">
-        <v>992.0480000000002</v>
+        <v>1006.592</v>
       </c>
       <c r="F94">
-        <v>1338.048</v>
+        <v>1352.592</v>
       </c>
       <c r="G94">
         <v>107.2</v>
@@ -8995,37 +8995,37 @@
         <v>116.1</v>
       </c>
       <c r="M94">
-        <v>315.5117184000001</v>
+        <v>318.9411936</v>
       </c>
       <c r="N94">
-        <v>-199.4117184</v>
+        <v>-202.8411936</v>
       </c>
       <c r="O94">
-        <v>-41.87646086400001</v>
+        <v>-42.59665065599999</v>
       </c>
       <c r="P94">
-        <v>-157.535257536</v>
+        <v>-160.244542944</v>
       </c>
       <c r="Q94">
-        <v>-94.73525753600002</v>
+        <v>-97.44454294399999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4706667808398676</v>
+        <v>0.5313620352455629</v>
       </c>
       <c r="T94">
-        <v>7.163864297758421</v>
+        <v>8.187273483152481</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07727446740691327</v>
+        <v>0.07644355915522603</v>
       </c>
       <c r="W94">
-        <v>0.2175786805854499</v>
+        <v>0.2177746087511977</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3679736543186346</v>
+        <v>0.3640169483582193</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2397257286058033</v>
+        <v>0.2416257286058033</v>
       </c>
       <c r="C95">
-        <v>-869.918091152274</v>
+        <v>-887.6889979771481</v>
       </c>
       <c r="D95">
-        <v>375.4739088477261</v>
+        <v>372.2470020228521</v>
       </c>
       <c r="E95">
-        <v>1006.592</v>
+        <v>1021.136</v>
       </c>
       <c r="F95">
-        <v>1352.592</v>
+        <v>1367.136</v>
       </c>
       <c r="G95">
         <v>107.2</v>
@@ -9077,37 +9077,37 @@
         <v>116.1</v>
       </c>
       <c r="M95">
-        <v>318.9411936</v>
+        <v>322.3706688</v>
       </c>
       <c r="N95">
-        <v>-202.8411936</v>
+        <v>-206.2706688</v>
       </c>
       <c r="O95">
-        <v>-42.59665065599999</v>
+        <v>-43.316840448</v>
       </c>
       <c r="P95">
-        <v>-160.244542944</v>
+        <v>-162.953828352</v>
       </c>
       <c r="Q95">
-        <v>-97.44454294399999</v>
+        <v>-100.153828352</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5313620352455629</v>
+        <v>0.6122890411198236</v>
       </c>
       <c r="T95">
-        <v>8.187273483152481</v>
+        <v>9.551819063677899</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07644355915522603</v>
+        <v>0.07563032980251086</v>
       </c>
       <c r="W95">
-        <v>0.2177746087511977</v>
+        <v>0.217966368232568</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3640169483582193</v>
+        <v>0.3601444276310042</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2416257286058033</v>
+        <v>0.2435257286058033</v>
       </c>
       <c r="C96">
-        <v>-887.6889979771481</v>
+        <v>-905.4049119040644</v>
       </c>
       <c r="D96">
-        <v>372.2470020228521</v>
+        <v>369.0750880959359</v>
       </c>
       <c r="E96">
-        <v>1021.136</v>
+        <v>1035.68</v>
       </c>
       <c r="F96">
-        <v>1367.136</v>
+        <v>1381.68</v>
       </c>
       <c r="G96">
         <v>107.2</v>
@@ -9159,37 +9159,37 @@
         <v>116.1</v>
       </c>
       <c r="M96">
-        <v>322.3706688</v>
+        <v>325.8001440000001</v>
       </c>
       <c r="N96">
-        <v>-206.2706688</v>
+        <v>-209.7001440000001</v>
       </c>
       <c r="O96">
-        <v>-43.316840448</v>
+        <v>-44.03703024000001</v>
       </c>
       <c r="P96">
-        <v>-162.953828352</v>
+        <v>-165.6631137600001</v>
       </c>
       <c r="Q96">
-        <v>-100.153828352</v>
+        <v>-102.8631137600001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6122890411198236</v>
+        <v>0.7255868493437886</v>
       </c>
       <c r="T96">
-        <v>9.551819063677899</v>
+        <v>11.46218287641348</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07563032980251086</v>
+        <v>0.07483422106774758</v>
       </c>
       <c r="W96">
-        <v>0.217966368232568</v>
+        <v>0.2181540906722251</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3601444276310042</v>
+        <v>0.3563534336559409</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2435257286058033</v>
+        <v>0.2454257286058033</v>
       </c>
       <c r="C97">
-        <v>-905.4049119040644</v>
+        <v>-923.0672268377898</v>
       </c>
       <c r="D97">
-        <v>369.0750880959359</v>
+        <v>365.9567731622103</v>
       </c>
       <c r="E97">
-        <v>1035.68</v>
+        <v>1050.224</v>
       </c>
       <c r="F97">
-        <v>1381.68</v>
+        <v>1396.224</v>
       </c>
       <c r="G97">
         <v>107.2</v>
@@ -9241,37 +9241,37 @@
         <v>116.1</v>
       </c>
       <c r="M97">
-        <v>325.8001440000001</v>
+        <v>329.2296192000001</v>
       </c>
       <c r="N97">
-        <v>-209.7001440000001</v>
+        <v>-213.1296192</v>
       </c>
       <c r="O97">
-        <v>-44.03703024000001</v>
+        <v>-44.75722003200001</v>
       </c>
       <c r="P97">
-        <v>-165.6631137600001</v>
+        <v>-168.372399168</v>
       </c>
       <c r="Q97">
-        <v>-102.8631137600001</v>
+        <v>-105.572399168</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7255868493437886</v>
+        <v>0.8955335616797361</v>
       </c>
       <c r="T97">
-        <v>11.46218287641348</v>
+        <v>14.32772859551686</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07483422106774758</v>
+        <v>0.07405469793162521</v>
       </c>
       <c r="W97">
-        <v>0.2181540906722251</v>
+        <v>0.2183379022277228</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3563534336559409</v>
+        <v>0.3526414187220249</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2454257286058033</v>
+        <v>0.2473257286058033</v>
       </c>
       <c r="C98">
-        <v>-923.0672268377896</v>
+        <v>-940.6772899693785</v>
       </c>
       <c r="D98">
-        <v>365.9567731622103</v>
+        <v>362.8907100306215</v>
       </c>
       <c r="E98">
-        <v>1050.224</v>
+        <v>1064.768</v>
       </c>
       <c r="F98">
-        <v>1396.224</v>
+        <v>1410.768</v>
       </c>
       <c r="G98">
         <v>107.2</v>
@@ -9323,37 +9323,37 @@
         <v>116.1</v>
       </c>
       <c r="M98">
-        <v>329.2296192</v>
+        <v>332.6590944</v>
       </c>
       <c r="N98">
-        <v>-213.1296192</v>
+        <v>-216.5590944</v>
       </c>
       <c r="O98">
-        <v>-44.75722003199999</v>
+        <v>-45.477409824</v>
       </c>
       <c r="P98">
-        <v>-168.372399168</v>
+        <v>-171.081684576</v>
       </c>
       <c r="Q98">
-        <v>-105.572399168</v>
+        <v>-108.281684576</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8955335616797337</v>
+        <v>1.178778082239645</v>
       </c>
       <c r="T98">
-        <v>14.32772859551682</v>
+        <v>19.10363812735576</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07405469793162524</v>
+        <v>0.07329124743748476</v>
       </c>
       <c r="W98">
-        <v>0.2183379022277228</v>
+        <v>0.2185179238542411</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3526414187220249</v>
+        <v>0.349005940178499</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2473257286058033</v>
+        <v>0.2492257286058033</v>
       </c>
       <c r="C99">
-        <v>-940.6772899693785</v>
+        <v>-958.2364037167977</v>
       </c>
       <c r="D99">
-        <v>362.8907100306215</v>
+        <v>359.8755962832025</v>
       </c>
       <c r="E99">
-        <v>1064.768</v>
+        <v>1079.312</v>
       </c>
       <c r="F99">
-        <v>1410.768</v>
+        <v>1425.312</v>
       </c>
       <c r="G99">
         <v>107.2</v>
@@ -9405,37 +9405,37 @@
         <v>116.1</v>
       </c>
       <c r="M99">
-        <v>332.6590944</v>
+        <v>336.0885696</v>
       </c>
       <c r="N99">
-        <v>-216.5590944</v>
+        <v>-219.9885696</v>
       </c>
       <c r="O99">
-        <v>-45.477409824</v>
+        <v>-46.197599616</v>
       </c>
       <c r="P99">
-        <v>-171.081684576</v>
+        <v>-173.790969984</v>
       </c>
       <c r="Q99">
-        <v>-108.281684576</v>
+        <v>-110.990969984</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.178778082239645</v>
+        <v>1.745267123359468</v>
       </c>
       <c r="T99">
-        <v>19.10363812735576</v>
+        <v>28.65545719103364</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07329124743748476</v>
+        <v>0.07254337756567368</v>
       </c>
       <c r="W99">
-        <v>0.2185179238542411</v>
+        <v>0.2186942715700142</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.349005940178499</v>
+        <v>0.3454446550746366</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2492257286058033</v>
+        <v>0.2511257286058032</v>
       </c>
       <c r="C100">
-        <v>-958.2364037167977</v>
+        <v>-975.745827569609</v>
       </c>
       <c r="D100">
-        <v>359.8755962832025</v>
+        <v>356.9101724303911</v>
       </c>
       <c r="E100">
-        <v>1079.312</v>
+        <v>1093.856</v>
       </c>
       <c r="F100">
-        <v>1425.312</v>
+        <v>1439.856</v>
       </c>
       <c r="G100">
         <v>107.2</v>
@@ -9487,37 +9487,37 @@
         <v>116.1</v>
       </c>
       <c r="M100">
-        <v>336.0885696</v>
+        <v>339.5180448</v>
       </c>
       <c r="N100">
-        <v>-219.9885696</v>
+        <v>-223.4180448</v>
       </c>
       <c r="O100">
-        <v>-46.197599616</v>
+        <v>-46.91778940799999</v>
       </c>
       <c r="P100">
-        <v>-173.790969984</v>
+        <v>-176.500255392</v>
       </c>
       <c r="Q100">
-        <v>-110.990969984</v>
+        <v>-113.700255392</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.745267123359468</v>
+        <v>3.444734246718935</v>
       </c>
       <c r="T100">
-        <v>28.65545719103364</v>
+        <v>57.31091438206729</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07254337756567368</v>
+        <v>0.07181061617612144</v>
       </c>
       <c r="W100">
-        <v>0.2186942715700142</v>
+        <v>0.2188670567056706</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3454446550746366</v>
+        <v>0.3419553151243878</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2511257286058032</v>
-      </c>
-      <c r="C101">
-        <v>-975.745827569609</v>
-      </c>
-      <c r="D101">
-        <v>356.9101724303911</v>
-      </c>
-      <c r="E101">
-        <v>1093.856</v>
-      </c>
-      <c r="F101">
-        <v>1439.856</v>
-      </c>
-      <c r="G101">
-        <v>107.2</v>
-      </c>
-      <c r="H101">
-        <v>1108.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>178.9</v>
-      </c>
-      <c r="K101">
-        <v>62.8</v>
-      </c>
-      <c r="L101">
-        <v>116.1</v>
-      </c>
-      <c r="M101">
-        <v>339.5180448</v>
-      </c>
-      <c r="N101">
-        <v>-223.4180448</v>
-      </c>
-      <c r="O101">
-        <v>-46.91778940799999</v>
-      </c>
-      <c r="P101">
-        <v>-176.500255392</v>
-      </c>
-      <c r="Q101">
-        <v>-113.700255392</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.444734246718935</v>
-      </c>
-      <c r="T101">
-        <v>57.31091438206729</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07181061617612144</v>
-      </c>
-      <c r="W101">
-        <v>0.2188670567056706</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3419553151243878</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
